--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,80 +480,200 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home_rival_team</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away_rival_team</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_val_player_start_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
@@ -562,249 +682,513 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45508.65625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45513.67708333334</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio partenio adriano lombardi
-  avellino </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26000</v>
+        <v>16917</v>
       </c>
       <c r="F2" t="n">
-        <v>5050</v>
+        <v>7139</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>57</v>
+      </c>
+      <c r="L2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>9</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>77</v>
+      </c>
+      <c r="V2" t="n">
+        <v>773</v>
+      </c>
+      <c r="W2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>A332L1f5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>hKSfjtsQ</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>773</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="X2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>4727272.727272728</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>68</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>983500</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>26.29166666666667</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>72.29166666666667</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5370833.333333333</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>185.3157894736842</v>
+      </c>
+      <c r="AU2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>182.8333333333333</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>67.16666666666667</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1137500</v>
-      </c>
-      <c r="T2" t="n">
-        <v>69</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1278947.368421053</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>71.36842105263158</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45508.64583333334</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45513.65625</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23860</v>
+        <v>36599</v>
       </c>
       <c r="F3" t="n">
-        <v>4468</v>
+        <v>22000</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>54</v>
+      </c>
+      <c r="L3" t="n">
+        <v>46</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>16</v>
+      </c>
+      <c r="R3" t="n">
+        <v>11</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>77</v>
+      </c>
+      <c r="V3" t="n">
+        <v>773</v>
+      </c>
+      <c r="W3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>xddf1qfh</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2gUwEtrE</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L3" t="n">
-        <v>773</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="X3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4072500</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>63.375</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>781250</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>26.53333333333333</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>184.0666666666667</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>72.26666666666667</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5316666.666666667</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>75.93333333333334</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>62.1875</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>718125</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>65.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45507.64583333334</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45513.5625</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vanni sanna
-  sassari </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12000</v>
+        <v>25144</v>
       </c>
       <c r="F4" t="n">
-        <v>2955</v>
+        <v>5850</v>
       </c>
       <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>62</v>
+      </c>
+      <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>UiGfvfvT</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>z7WK5Pwb</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="Q4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>WE57Jh0D</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
         <v>77</v>
       </c>
-      <c r="L4" t="n">
+      <c r="V4" t="n">
         <v>773</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="n">
-        <v>28</v>
-      </c>
-      <c r="P4" t="n">
-        <v>176</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>587500</v>
-      </c>
-      <c r="T4" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>181.6</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1820000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>70.2</v>
-      </c>
+        <v>20242025</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4663636.363636363</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>25.40909090909091</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4140909.090909091</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45507.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45513.54166666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dei marmi
-  carrara </t>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5280</v>
+        <v>21525</v>
       </c>
       <c r="F5" t="n">
-        <v>1707</v>
+        <v>2000</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -814,50 +1198,130 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4rwnnbnB</t>
+          <t>C0yUqo8c</t>
         </is>
       </c>
       <c r="K5" t="n">
+        <v>49</v>
+      </c>
+      <c r="L5" t="n">
+        <v>51</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
+      </c>
+      <c r="R5" t="n">
+        <v>9</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
         <v>77</v>
       </c>
-      <c r="L5" t="n">
+      <c r="V5" t="n">
         <v>773</v>
       </c>
-      <c r="M5" t="n">
+      <c r="W5" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
+      <c r="X5" t="n">
         <v>20242025</v>
       </c>
-      <c r="O5" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>179.8</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>21.60869565217391</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>184.2608695652174</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>68.08695652173913</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3495652.173913043</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>78.26086956521739</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>26.22727272727273</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>184.7727272727273</v>
+      </c>
+      <c r="AU5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>775000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>65.31818181818181</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1042954.545454545</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>69.13636363636364</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:BN31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,848 +480,5978 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>ball_possession_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ball_possession_away</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_away</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>fouls_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fouls_away</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45522.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16917</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7139</v>
-      </c>
+        <v>16416</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>W02MZDnp</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="K2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>43</v>
+      </c>
+      <c r="N2" t="n">
         <v>57</v>
       </c>
-      <c r="L2" t="n">
-        <v>43</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
+      <c r="S2" t="n">
+        <v>15</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>77</v>
+      </c>
+      <c r="X2" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4581818.181818182</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>76.09090909090909</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>78</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>19037500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>81</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>184</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2293750</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>24.78947368421053</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>180.421052631579</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.894736842105263</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>77.21052631578948</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>24271052.63157895</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>82.21052631578948</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>15</v>
-      </c>
-      <c r="R2" t="n">
-        <v>9</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>bmzifXwb</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>77</v>
-      </c>
-      <c r="V2" t="n">
-        <v>773</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>25.63636363636364</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>183.9090909090909</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.454545454545455</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>72.27272727272727</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>4727272.727272728</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>76.54545454545455</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>182.6</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>68</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>983500</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>26.29166666666667</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>180.875</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>72.29166666666667</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5370833.333333333</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>75.375</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>23.57894736842105</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>185.3157894736842</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>65.26315789473684</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1278947.368421053</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>71.36842105263158</v>
+      <c r="BE2" t="n">
+        <v>288</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>12300000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>292</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>78</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45522.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F3" t="n">
-        <v>22000</v>
-      </c>
+        <v>70634</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>54</v>
+        <v>2.43</v>
       </c>
       <c r="L3" t="n">
-        <v>46</v>
+        <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="O3" t="n">
         <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="n">
         <v>11</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
         <v>77</v>
       </c>
-      <c r="V3" t="n">
-        <v>773</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
       <c r="X3" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>183.9</v>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>26.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>72.3</v>
+        <v>182.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>4072500</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>75.8</v>
+        <v>79</v>
       </c>
       <c r="AG3" t="n">
+        <v>20770000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AI3" t="n">
         <v>26</v>
       </c>
-      <c r="AH3" t="n">
-        <v>183.875</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>63.375</v>
+        <v>183.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>781250</v>
+        <v>1.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>68.875</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>26.53333333333333</v>
+        <v>2240000</v>
       </c>
       <c r="AN3" t="n">
-        <v>184.0666666666667</v>
+        <v>74.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.533333333333333</v>
+        <v>24.70833333333333</v>
       </c>
       <c r="AP3" t="n">
-        <v>72.26666666666667</v>
+        <v>182.375</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5316666.666666667</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="AR3" t="n">
-        <v>75.93333333333334</v>
+        <v>74.45833333333333</v>
       </c>
       <c r="AS3" t="n">
-        <v>25.4375</v>
+        <v>11406250</v>
       </c>
       <c r="AT3" t="n">
-        <v>179.875</v>
+        <v>79</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>24.47619047619047</v>
       </c>
       <c r="AV3" t="n">
-        <v>62.1875</v>
+        <v>181.7619047619048</v>
       </c>
       <c r="AW3" t="n">
-        <v>718125</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>65.75</v>
+        <v>66.52380952380952</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1505714.285714286</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>72.42857142857143</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>423</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>19125000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>4xHh663n</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45522.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">scatena g 
+          <t xml:space="preserve">caputi m 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
+        <v>38279</v>
       </c>
       <c r="F4" t="n">
-        <v>5850</v>
+        <v>26418</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M4" t="n">
+        <v>74</v>
+      </c>
+      <c r="N4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O4" t="n">
+        <v>22</v>
+      </c>
+      <c r="P4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="n">
+        <v>13</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>77</v>
+      </c>
+      <c r="X4" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>A332L1f5</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>62</v>
-      </c>
-      <c r="L4" t="n">
-        <v>38</v>
-      </c>
-      <c r="M4" t="n">
-        <v>16</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>WE57Jh0D</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>77</v>
-      </c>
-      <c r="V4" t="n">
-        <v>773</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
+        <v>25.27272727272727</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>186.1818181818182</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>8381818.181818182</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>79.09090909090909</v>
+      </c>
+      <c r="AI4" t="n">
         <v>25.45454545454545</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AJ4" t="n">
         <v>184.8181818181818</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
         <v>73.45454545454545</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AM4" t="n">
         <v>4663636.363636363</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AN4" t="n">
         <v>76.27272727272727</v>
       </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>25.40909090909091</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>183.8636363636364</v>
-      </c>
       <c r="AO4" t="n">
-        <v>1.045454545454545</v>
+        <v>23.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>71.81818181818181</v>
+        <v>183.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4140909.090909091</v>
+        <v>1.15</v>
       </c>
       <c r="AR4" t="n">
-        <v>75.90909090909091</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5271250</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3143750</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>74.5625</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>37325000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>393</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>149</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>20800000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>6RvR2hEi</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45522.5625</v>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>68</v>
+      </c>
+      <c r="O5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="n">
+        <v>13</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>77</v>
+      </c>
+      <c r="X5" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>185.375</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5012500</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>31620000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>23.95238095238095</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>70.04761904761905</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3560714.285714286</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>75.61904761904762</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>24.41176470588235</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>182.1764705882353</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.411764705882353</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>76.05882352941177</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>16613235.29411765</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>79.58823529411765</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>186</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>66</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0lGMiS5j</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maresca f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M6" t="n">
+        <v>56</v>
+      </c>
+      <c r="N6" t="n">
+        <v>44</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>40727272.72727273</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>84.54545454545455</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>23.31578947368421</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>181.2631578947368</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>79</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>30031578.94736842</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>84.21052631578948</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>23.89473684210526</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>185.6315789473684</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.105263157894737</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>71.94736842105263</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7406578.947368421</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>77.47368421052632</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>31</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>192</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>77</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>287</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>49600000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>hKOA02XN</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45521.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M7" t="n">
+        <v>39</v>
+      </c>
+      <c r="N7" t="n">
+        <v>61</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>19</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>23.72727272727273</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3172727.272727273</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>71.45454545454545</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>76.90909090909091</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>68.91666666666667</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2695416.666666667</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>75.20833333333333</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>26.47619047619047</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>72.47619047619048</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5076190.476190476</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>75.80952380952381</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>347</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>11825000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>363</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>224</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>O2Fteteo</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M8" t="n">
+        <v>32</v>
+      </c>
+      <c r="N8" t="n">
+        <v>68</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>28.36363636363636</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.454545454545455</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>43272727.27272727</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>85.36363636363636</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>26.70588235294118</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>184.4117647058823</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.352941176470588</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>70.64705882352941</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3080882.352941176</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>25.82608695652174</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>182.7826086956522</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.782608695652174</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>78.95652173913044</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>26208695.65217391</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>82</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>188</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>258</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4850000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>295</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>236</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>53800000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Sf88FVcc</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45521.5625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M9" t="n">
+        <v>39</v>
+      </c>
+      <c r="N9" t="n">
+        <v>61</v>
+      </c>
+      <c r="O9" t="n">
+        <v>13</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3555555.555555556</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>13710000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>22.73913043478261</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>180.5217391304348</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>66.73913043478261</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2866956.52173913</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>22.68181818181818</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>180.4545454545455</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.409090909090909</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>73.13636363636364</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11150000</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>80.77272727272727</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>355</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>373</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45516.67708333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>53</v>
+      </c>
+      <c r="N10" t="n">
+        <v>47</v>
+      </c>
+      <c r="O10" t="n">
+        <v>21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4015909.090909091</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>74.72727272727273</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>23.92307692307692</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>183.9230769230769</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.230769230769231</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>68.42307692307692</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3002884.615384615</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>74.65384615384616</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45516.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rutella d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6905</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>59</v>
+      </c>
+      <c r="N11" t="n">
+        <v>41</v>
+      </c>
+      <c r="O11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>13</v>
+      </c>
+      <c r="T11" t="n">
+        <v>17</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4894444.444444444</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>75.88888888888889</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>186.3</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1295000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>24.10526315789474</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>182.8421052631579</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>67.63157894736842</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2236842.105263158</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>74.47368421052632</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>24.27777777777778</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>183.5555555555555</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>66.83333333333333</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1538888.888888889</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>73.05555555555556</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>42SH31wI</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45516.5625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>38</v>
+      </c>
+      <c r="N12" t="n">
+        <v>62</v>
+      </c>
+      <c r="O12" t="n">
+        <v>19</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>77</v>
+      </c>
+      <c r="X12" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>181.2777777777778</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2694444.444444444</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9384</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>59</v>
+      </c>
+      <c r="N13" t="n">
+        <v>41</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
+        <v>19</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>77</v>
+      </c>
+      <c r="X13" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1597222.222222222</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>20.66666666666667</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>185.5333333333333</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>61.86666666666667</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>980000</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1611000</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45515.67708333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12035</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
+      <c r="N14" t="n">
+        <v>40</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>77</v>
+      </c>
+      <c r="X14" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11290000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1167500</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>23.57894736842105</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>184.4736842105263</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>70.05263157894737</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>5423684.210526315</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>76.47368421052632</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>22.28571428571428</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>179.7142857142857</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>64.14285714285714</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1171428.571428571</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>71.85714285714286</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45515.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14196</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>43</v>
+      </c>
+      <c r="N15" t="n">
+        <v>57</v>
+      </c>
+      <c r="O15" t="n">
+        <v>11</v>
+      </c>
+      <c r="P15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>77</v>
+      </c>
+      <c r="X15" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>181.7777777777778</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>70.33333333333333</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2136111.111111111</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>181.85</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1749750</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>28.04545454545455</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>183.8636363636364</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>70.59090909090909</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3314318.181818182</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>71.68181818181819</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5034</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>47</v>
+      </c>
+      <c r="N16" t="n">
+        <v>53</v>
+      </c>
+      <c r="O16" t="n">
+        <v>17</v>
+      </c>
+      <c r="P16" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>12</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>77</v>
+      </c>
+      <c r="X16" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2345000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>22.95238095238095</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>183.1904761904762</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>67.04761904761905</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2280476.19047619</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>24.82608695652174</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>183.9130434782609</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>69.26086956521739</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>2280434.782608696</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>74.26086956521739</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4310</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>38</v>
+      </c>
+      <c r="N17" t="n">
+        <v>62</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9</v>
+      </c>
+      <c r="P17" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="n">
+        <v>12</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>77</v>
+      </c>
+      <c r="X17" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1888888.888888889</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>181.6111111111111</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1217777.777777778</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>23.47368421052632</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>184.2631578947368</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>66.78947368421052</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1748421.052631579</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>73.42105263157895</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F18" t="n">
+        <v>52000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>70</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O18" t="n">
+        <v>28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>77</v>
+      </c>
+      <c r="X18" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>26.72727272727273</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>182.0909090909091</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>80.72727272727273</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>32290909.09090909</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>82.36363636363636</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1382500</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>182.65</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9576250</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>23.78571428571428</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>63.85714285714285</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1024642.857142857</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>69.64285714285714</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1738</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>57</v>
+      </c>
+      <c r="N19" t="n">
+        <v>43</v>
+      </c>
+      <c r="O19" t="n">
+        <v>22</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>10</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>77</v>
+      </c>
+      <c r="X19" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>185</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3150000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>28.22222222222222</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>67.88888888888889</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1133333.333333333</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>69.88888888888889</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>181.4090909090909</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>67.45454545454545</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2088181.818181818</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1014583.333333333</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>02s0k9od</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45514.5625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>39211</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7048</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>54</v>
+      </c>
+      <c r="N20" t="n">
+        <v>46</v>
+      </c>
+      <c r="O20" t="n">
+        <v>11</v>
+      </c>
+      <c r="P20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>14</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>77</v>
+      </c>
+      <c r="X20" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>184.1111111111111</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>5011111.111111111</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>184.0555555555555</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2776388.888888889</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>74.05555555555556</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45514.54166666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3724</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>58</v>
+      </c>
+      <c r="N21" t="n">
+        <v>42</v>
+      </c>
+      <c r="O21" t="n">
+        <v>13</v>
+      </c>
+      <c r="P21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>12</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>77</v>
+      </c>
+      <c r="X21" t="n">
+        <v>773</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>26.09090909090909</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>184.5454545454545</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2154545.454545455</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>25.30434782608696</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>69.08695652173913</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2065217.391304348</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>182.2083333333333</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>64.29166666666667</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1022500</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>69.54166666666667</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>14650</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>49</v>
+      </c>
+      <c r="N22" t="n">
+        <v>51</v>
+      </c>
+      <c r="O22" t="n">
+        <v>9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>77</v>
+      </c>
+      <c r="X22" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1030555.555555556</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>24.54545454545455</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>5297727.272727272</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>985000</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>2540000</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11382</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>42</v>
+      </c>
+      <c r="N23" t="n">
+        <v>58</v>
+      </c>
+      <c r="O23" t="n">
+        <v>14</v>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>14</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>77</v>
+      </c>
+      <c r="X23" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3056250</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>62.875</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>871875</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6840</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>32</v>
+      </c>
+      <c r="N24" t="n">
+        <v>68</v>
+      </c>
+      <c r="O24" t="n">
+        <v>15</v>
+      </c>
+      <c r="P24" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>11</v>
+      </c>
+      <c r="T24" t="n">
+        <v>16</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>77</v>
+      </c>
+      <c r="X24" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1165000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>186.0909090909091</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1909090.909090909</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>64.375</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1179687.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>23.91666666666667</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>2183333.333333333</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>45</v>
+      </c>
+      <c r="N25" t="n">
+        <v>55</v>
+      </c>
+      <c r="O25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P25" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>12</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
+        <v>13</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>77</v>
+      </c>
+      <c r="X25" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1646875</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>181.4444444444445</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1680555.555555556</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>21.78260869565218</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>63.91304347826087</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1310869.565217391</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>74.04347826086956</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>24.42857142857143</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>67.76190476190476</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1782142.857142857</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>73.28571428571429</v>
+      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">mapei stadium – citta del tricolore
   reggio emilia </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E26" t="n">
         <v>21525</v>
       </c>
-      <c r="F5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>QDdvI0zl</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>30</v>
+      </c>
+      <c r="N26" t="n">
+        <v>70</v>
+      </c>
+      <c r="O26" t="n">
+        <v>12</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="n">
+        <v>25</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>77</v>
+      </c>
+      <c r="X26" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>939000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>182.8947368421053</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>65.26315789473684</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1195000</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>69.36842105263158</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20957</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>56</v>
+      </c>
+      <c r="N27" t="n">
+        <v>44</v>
+      </c>
+      <c r="O27" t="n">
+        <v>16</v>
+      </c>
+      <c r="P27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="n">
+        <v>14</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>77</v>
+      </c>
+      <c r="X27" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1541666.666666667</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>181.68</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>64.12</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>934600</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8770</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>54</v>
+      </c>
+      <c r="N28" t="n">
+        <v>46</v>
+      </c>
+      <c r="O28" t="n">
+        <v>19</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="n">
+        <v>22</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>77</v>
+      </c>
+      <c r="X28" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1697500</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1563888.888888889</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>72.11111111111111</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>22.80952380952381</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>184.2380952380952</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>64.80952380952381</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1483333.333333333</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>72.14285714285714</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>25.05882352941176</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>186.0588235294118</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>66.41176470588235</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1320588.235294118</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>71.94117647058823</v>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12509</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>C0yUqo8c</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>49</v>
-      </c>
-      <c r="L5" t="n">
-        <v>51</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>70</v>
+      </c>
+      <c r="N29" t="n">
+        <v>30</v>
+      </c>
+      <c r="O29" t="n">
         <v>15</v>
       </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="P29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>23</v>
+      </c>
+      <c r="T29" t="n">
+        <v>12</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>77</v>
+      </c>
+      <c r="X29" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2572222.222222222</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>65.125</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>22.72222222222222</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>178.0555555555555</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1901388.888888889</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>74.61111111111111</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>26.84210526315789</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>182.7368421052632</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>844473.6842105263</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>68.47368421052632</v>
+      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>68</v>
+      </c>
+      <c r="N30" t="n">
+        <v>32</v>
+      </c>
+      <c r="O30" t="n">
         <v>9</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P30" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="n">
         <v>15</v>
       </c>
-      <c r="R5" t="n">
-        <v>9</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
         <v>77</v>
       </c>
-      <c r="V5" t="n">
-        <v>773</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="X30" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
         <v>20242025</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>0M9xNN8N</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>24.54545454545455</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>185.1818181818182</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>71.36363636363636</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>5297727.272727272</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>21.60869565217391</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>184.2608695652174</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.043478260869565</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>68.08695652173913</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3495652.173913043</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>78.26086956521739</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>26.22727272727273</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>184.7727272727273</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>65.31818181818181</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1042954.545454545</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>69.13636363636364</v>
-      </c>
+      <c r="AC30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>951000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>26.45454545454545</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>66.81818181818181</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1190909.090909091</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>69.72727272727273</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>185.3888888888889</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>65.44444444444444</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1131944.444444444</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>24.92307692307692</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>180.5384615384615</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.076923076923077</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>65.61538461538461</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1168846.153846154</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>70.46153846153847</v>
+      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45520.64583333334</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5317</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>37</v>
+      </c>
+      <c r="N31" t="n">
+        <v>63</v>
+      </c>
+      <c r="O31" t="n">
+        <v>18</v>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="n">
+        <v>10</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>77</v>
+      </c>
+      <c r="X31" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>3020000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>23.21428571428572</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>181.2142857142857</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>64.71428571428571</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1164285.714285714</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>75.41666666666667</v>
+      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:BN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,847 +480,721 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>ball_possession_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ball_possession_away</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_away</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>fouls_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fouls_away</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45523.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16917</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7139</v>
-      </c>
+        <v>41507</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M2" t="n">
+        <v>55</v>
+      </c>
+      <c r="N2" t="n">
+        <v>45</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>77</v>
+      </c>
+      <c r="X2" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>W02MZDnp</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>57</v>
-      </c>
-      <c r="L2" t="n">
-        <v>43</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="AC2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>186.125</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>28437500</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>83.125</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5062500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>18218750</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>185</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3786250</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>15</v>
-      </c>
-      <c r="R2" t="n">
-        <v>9</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>bmzifXwb</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>77</v>
-      </c>
-      <c r="V2" t="n">
-        <v>773</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="BE2" t="n">
+        <v>321</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>334</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>187</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>1</v>
       </c>
-      <c r="X2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>25.63636363636364</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>183.9090909090909</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.454545454545455</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>72.27272727272727</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>4727272.727272728</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>76.54545454545455</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>182.6</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>68</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>983500</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>26.29166666666667</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>180.875</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>72.29166666666667</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5370833.333333333</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>75.375</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>23.57894736842105</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>185.3157894736842</v>
-      </c>
-      <c r="AU2" t="n">
+      <c r="BK2" t="n">
         <v>1</v>
       </c>
-      <c r="AV2" t="n">
-        <v>65.26315789473684</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1278947.368421053</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>71.36842105263158</v>
+      <c r="BL2" t="n">
+        <v>73</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45523.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">massa d 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36599</v>
+        <v>40670</v>
       </c>
       <c r="F3" t="n">
-        <v>22000</v>
+        <v>28719</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M3" t="n">
+        <v>47</v>
+      </c>
+      <c r="N3" t="n">
+        <v>53</v>
+      </c>
+      <c r="O3" t="n">
+        <v>19</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>24</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>77</v>
+      </c>
+      <c r="X3" t="n">
+        <v>771</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6ulJbMCe</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>54</v>
-      </c>
-      <c r="L3" t="n">
-        <v>46</v>
-      </c>
-      <c r="M3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O3" t="n">
-        <v>13</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>16</v>
-      </c>
-      <c r="R3" t="n">
-        <v>11</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>77</v>
-      </c>
-      <c r="V3" t="n">
-        <v>773</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AF3" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>77.875</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>188</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>13650000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>22.68421052631579</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>181.6842105263158</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>1</v>
       </c>
-      <c r="X3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>183.9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>4072500</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>183.875</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>63.375</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>781250</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>68.875</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>26.53333333333333</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>184.0666666666667</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.533333333333333</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>72.26666666666667</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5316666.666666667</v>
-      </c>
       <c r="AR3" t="n">
-        <v>75.93333333333334</v>
+        <v>67.63157894736842</v>
       </c>
       <c r="AS3" t="n">
-        <v>25.4375</v>
+        <v>2952631.578947369</v>
       </c>
       <c r="AT3" t="n">
-        <v>179.875</v>
+        <v>75.31578947368421</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AV3" t="n">
-        <v>62.1875</v>
+        <v>185.7692307692308</v>
       </c>
       <c r="AW3" t="n">
-        <v>718125</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AX3" t="n">
-        <v>65.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dnnqk0iD</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45513.5625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">scatena g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5850</v>
-      </c>
-      <c r="G4" t="n">
+        <v>73.23076923076923</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9996923.076923076</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>78.76923076923077</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>215</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>232</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BK3" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>A332L1f5</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>62</v>
-      </c>
-      <c r="L4" t="n">
-        <v>38</v>
-      </c>
-      <c r="M4" t="n">
-        <v>16</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15</v>
-      </c>
-      <c r="R4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>WE57Jh0D</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>77</v>
-      </c>
-      <c r="V4" t="n">
-        <v>773</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
-        <v>25.45454545454545</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>184.8181818181818</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>73.45454545454545</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>4663636.363636363</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>76.27272727272727</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>25.40909090909091</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>183.8636363636364</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1.045454545454545</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>71.81818181818181</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4140909.090909091</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>75.90909090909091</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>QT6wuRFc</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45513.54166666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>21525</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>QDdvI0zl</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>C0yUqo8c</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>49</v>
-      </c>
-      <c r="L5" t="n">
-        <v>51</v>
-      </c>
-      <c r="M5" t="n">
-        <v>15</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>9</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R5" t="n">
-        <v>9</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>77</v>
-      </c>
-      <c r="V5" t="n">
-        <v>773</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>24.54545454545455</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>185.1818181818182</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>71.36363636363636</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>5297727.272727272</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>21.60869565217391</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>184.2608695652174</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.043478260869565</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>68.08695652173913</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3495652.173913043</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>78.26086956521739</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>26.22727272727273</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>184.7727272727273</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>65.31818181818181</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1042954.545454545</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>69.13636363636364</v>
+      <c r="BL3" t="n">
+        <v>314</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>74000000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,82 +762,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">marcenaro m 
+          <t xml:space="preserve">sacchi j  l 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz stadium
-  turin </t>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>41507</v>
+        <v>27906</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="L2" t="n">
-        <v>0.18</v>
+        <v>2.21</v>
       </c>
       <c r="M2" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,210 +854,208 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>Iw7eKK25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
       <c r="AC2" t="n">
-        <v>24</v>
+        <v>22.44444444444444</v>
       </c>
       <c r="AD2" t="n">
-        <v>186.125</v>
+        <v>184.7777777777778</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>78.75</v>
+        <v>69.55555555555556</v>
       </c>
       <c r="AG2" t="n">
-        <v>28437500</v>
+        <v>3555555.555555556</v>
       </c>
       <c r="AH2" t="n">
-        <v>83.125</v>
+        <v>77.33333333333333</v>
       </c>
       <c r="AI2" t="n">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>179.75</v>
+        <v>184.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.375</v>
+        <v>1.9</v>
       </c>
       <c r="AL2" t="n">
-        <v>72.375</v>
+        <v>81.7</v>
       </c>
       <c r="AM2" t="n">
-        <v>5062500</v>
+        <v>44650000</v>
       </c>
       <c r="AN2" t="n">
-        <v>74.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AO2" t="n">
-        <v>25.125</v>
+        <v>23.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>182.875</v>
+        <v>181</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AR2" t="n">
-        <v>77</v>
+        <v>68.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>18218750</v>
+        <v>3159500</v>
       </c>
       <c r="AT2" t="n">
-        <v>81.75</v>
+        <v>75.05</v>
       </c>
       <c r="AU2" t="n">
-        <v>27.15</v>
+        <v>23.53333333333333</v>
       </c>
       <c r="AV2" t="n">
-        <v>185</v>
+        <v>179.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.3</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="AX2" t="n">
-        <v>71.15000000000001</v>
+        <v>78.13333333333334</v>
       </c>
       <c r="AY2" t="n">
-        <v>3786250</v>
+        <v>22640000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.45</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>185.25</v>
+        <v>188.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.75</v>
+        <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="BF2" t="n">
-        <v>103000000</v>
+        <v>13400000</v>
       </c>
       <c r="BG2" t="n">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="BH2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="BI2" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK2" t="n">
         <v>1</v>
       </c>
       <c r="BL2" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="BM2" t="n">
-        <v>3200000</v>
+        <v>5500000</v>
       </c>
       <c r="BN2" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45523.5625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
+          <t xml:space="preserve">doveri d 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40670</v>
-      </c>
-      <c r="F3" t="n">
-        <v>28719</v>
-      </c>
+        <v>25144</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="K3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L3" t="n">
         <v>1.17</v>
       </c>
-      <c r="L3" t="n">
-        <v>2.04</v>
-      </c>
       <c r="M3" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="n">
         <v>10</v>
       </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="n">
-        <v>24</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1074,128 +1072,490 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>183.125</v>
+        <v>185.3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>71.875</v>
+        <v>73.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>5475000</v>
+        <v>4430000</v>
       </c>
       <c r="AH3" t="n">
-        <v>77.875</v>
+        <v>76.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>26.3</v>
+        <v>27.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>188</v>
+        <v>183.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>76.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="AM3" t="n">
-        <v>13650000</v>
+        <v>19270000</v>
       </c>
       <c r="AN3" t="n">
-        <v>80.2</v>
+        <v>80.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>22.68421052631579</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>181.6842105263158</v>
+        <v>184</v>
       </c>
       <c r="AQ3" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>71.82608695652173</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3582608.695652174</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>75.04347826086956</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>25.04166666666667</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>182.0416666666667</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>74.54166666666667</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11072916.66666667</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>78.70833333333333</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>181</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>20100000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>155</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>1</v>
       </c>
-      <c r="AR3" t="n">
-        <v>67.63157894736842</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2952631.578947369</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>75.31578947368421</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>185.7692307692308</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.153846153846154</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>73.23076923076923</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9996923.076923076</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>78.76923076923077</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>24.33333333333333</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>182</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45528.60416666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perenzoni d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="BE3" t="n">
-        <v>215</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>11100000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>232</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>189.25</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BK3" t="n">
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>40</v>
+      </c>
+      <c r="N4" t="n">
+        <v>60</v>
+      </c>
+      <c r="O4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="n">
+        <v>9</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>77</v>
+      </c>
+      <c r="X4" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1108500</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>26.38095238095238</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>185.5238095238095</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>66.57142857142857</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1147619.047619048</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>69.66666666666667</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>23.23076923076923</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>178.3846153846154</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>67.07692307692308</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1959615.384615385</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>74.53846153846153</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45527.64583333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scatena g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto braglia
+  modena </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>21092</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10248</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>41</v>
+      </c>
+      <c r="N5" t="n">
+        <v>59</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
         <v>4</v>
       </c>
-      <c r="BL3" t="n">
-        <v>314</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>74000000</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>329</v>
-      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>13</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>77</v>
+      </c>
+      <c r="X5" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1387500</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1470000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>26.95454545454545</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>183.3636363636364</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>67.27272727272727</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1215681.818181818</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>181.7826086956522</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.130434782608696</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>64.73913043478261</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1059347.826086957</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>69.47826086956522</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,82 +762,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio ennio tardini
-  parma </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27906</v>
+        <v>43147</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="L2" t="n">
-        <v>2.21</v>
+        <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
         <v>7</v>
       </c>
-      <c r="P2" t="n">
-        <v>16</v>
-      </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,154 +854,156 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>22.44444444444444</v>
+        <v>25.44444444444444</v>
       </c>
       <c r="AD2" t="n">
-        <v>184.7777777777778</v>
+        <v>185.4444444444445</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.55555555555556</v>
+        <v>75.66666666666667</v>
       </c>
       <c r="AG2" t="n">
-        <v>3555555.555555556</v>
+        <v>13922222.22222222</v>
       </c>
       <c r="AH2" t="n">
-        <v>77.33333333333333</v>
+        <v>80.33333333333333</v>
       </c>
       <c r="AI2" t="n">
-        <v>24.5</v>
+        <v>25.63636363636364</v>
       </c>
       <c r="AJ2" t="n">
-        <v>184.1</v>
+        <v>183.0909090909091</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.9</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AL2" t="n">
-        <v>81.7</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>44650000</v>
+        <v>2300000</v>
       </c>
       <c r="AN2" t="n">
-        <v>85.40000000000001</v>
+        <v>74.63636363636364</v>
       </c>
       <c r="AO2" t="n">
-        <v>23.5</v>
+        <v>23.60869565217391</v>
       </c>
       <c r="AP2" t="n">
-        <v>181</v>
+        <v>182.0869565217391</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.15</v>
+        <v>1.347826086956522</v>
       </c>
       <c r="AR2" t="n">
-        <v>68.8</v>
+        <v>74.21739130434783</v>
       </c>
       <c r="AS2" t="n">
-        <v>3159500</v>
+        <v>11895652.17391304</v>
       </c>
       <c r="AT2" t="n">
-        <v>75.05</v>
+        <v>80.56521739130434</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.53333333333333</v>
+        <v>23.52173913043478</v>
       </c>
       <c r="AV2" t="n">
-        <v>179.4</v>
+        <v>184.1304347826087</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.266666666666667</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>78.13333333333334</v>
+        <v>66.47826086956522</v>
       </c>
       <c r="AY2" t="n">
-        <v>22640000</v>
+        <v>1631304.347826087</v>
       </c>
       <c r="AZ2" t="n">
-        <v>82.59999999999999</v>
+        <v>73.65217391304348</v>
       </c>
       <c r="BA2" t="n">
-        <v>26.6</v>
+        <v>25.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>188.2</v>
+        <v>185.5</v>
       </c>
       <c r="BC2" t="n">
         <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BE2" t="n">
-        <v>354</v>
+        <v>155</v>
       </c>
       <c r="BF2" t="n">
-        <v>13400000</v>
+        <v>30500000</v>
       </c>
       <c r="BG2" t="n">
-        <v>365</v>
+        <v>160</v>
       </c>
       <c r="BH2" t="n">
-        <v>31</v>
+        <v>26.75</v>
       </c>
       <c r="BI2" t="n">
-        <v>192</v>
+        <v>178.75</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL2" t="n">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="BM2" t="n">
-        <v>5500000</v>
+        <v>14625000</v>
       </c>
       <c r="BN2" t="n">
-        <v>77</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">doveri d 
+          <t xml:space="preserve">rapuano a 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25144</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>28177</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20451</v>
+      </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
@@ -1010,52 +1012,52 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.92</v>
+        <v>2.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17</v>
+        <v>3.51</v>
       </c>
       <c r="M3" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="N3" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="O3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>5</v>
-      </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1072,211 +1074,215 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>25.5</v>
+        <v>26.88888888888889</v>
       </c>
       <c r="AD3" t="n">
-        <v>185.3</v>
+        <v>185.7777777777778</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF3" t="n">
-        <v>73.3</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="AG3" t="n">
-        <v>4430000</v>
+        <v>10711111.11111111</v>
       </c>
       <c r="AH3" t="n">
-        <v>76.2</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="AI3" t="n">
-        <v>27.1</v>
+        <v>25.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>183.2</v>
+        <v>188</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>79</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>19270000</v>
+        <v>15600000</v>
       </c>
       <c r="AN3" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>23.29411764705882</v>
       </c>
       <c r="AP3" t="n">
         <v>184</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.043478260869565</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>71.82608695652173</v>
+        <v>70.41176470588235</v>
       </c>
       <c r="AS3" t="n">
-        <v>3582608.695652174</v>
+        <v>5413235.294117647</v>
       </c>
       <c r="AT3" t="n">
-        <v>75.04347826086956</v>
+        <v>76.23529411764706</v>
       </c>
       <c r="AU3" t="n">
-        <v>25.04166666666667</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AV3" t="n">
-        <v>182.0416666666667</v>
+        <v>188.1111111111111</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>74.54166666666667</v>
+        <v>73.44444444444444</v>
       </c>
       <c r="AY3" t="n">
-        <v>11072916.66666667</v>
+        <v>10795555.55555556</v>
       </c>
       <c r="AZ3" t="n">
-        <v>78.70833333333333</v>
+        <v>79.11111111111111</v>
       </c>
       <c r="BA3" t="n">
-        <v>26.5</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="BB3" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="BF3" t="n">
-        <v>20100000</v>
+        <v>47500000</v>
       </c>
       <c r="BG3" t="n">
-        <v>155</v>
+        <v>244</v>
       </c>
       <c r="BH3" t="n">
-        <v>23</v>
+        <v>26.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>181.5</v>
+        <v>189.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="BK3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BL3" t="n">
-        <v>140</v>
+        <v>314</v>
       </c>
       <c r="BM3" t="n">
-        <v>6700000</v>
+        <v>74000000</v>
       </c>
       <c r="BN3" t="n">
-        <v>150</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.60416666666</v>
+        <v>45528.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">perenzoni d 
+          <t xml:space="preserve">di marco d 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marco druso
-  bolzano </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5539</v>
+        <v>80018</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N4" t="n">
+        <v>39</v>
+      </c>
+      <c r="O4" t="n">
+        <v>11</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>W02MZDnp</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Mq05g4BP</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>40</v>
-      </c>
-      <c r="N4" t="n">
-        <v>60</v>
-      </c>
-      <c r="O4" t="n">
-        <v>17</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
-        <v>7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>15</v>
-      </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>OjWmexQb</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>77</v>
       </c>
       <c r="X4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1286,173 +1292,215 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>182.4</v>
+        <v>182.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>67.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>1108500</v>
+        <v>38100000</v>
       </c>
       <c r="AH4" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+        <v>84.8</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>71.88888888888889</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5477777.777777778</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>78.11111111111111</v>
+      </c>
       <c r="AO4" t="n">
-        <v>26.38095238095238</v>
+        <v>26.07692307692308</v>
       </c>
       <c r="AP4" t="n">
-        <v>185.5238095238095</v>
+        <v>184.2692307692308</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.142857142857143</v>
+        <v>1.807692307692308</v>
       </c>
       <c r="AR4" t="n">
-        <v>66.57142857142857</v>
+        <v>78.76923076923077</v>
       </c>
       <c r="AS4" t="n">
-        <v>1147619.047619048</v>
+        <v>23684615.38461538</v>
       </c>
       <c r="AT4" t="n">
-        <v>69.66666666666667</v>
+        <v>81.84615384615384</v>
       </c>
       <c r="AU4" t="n">
-        <v>23.23076923076923</v>
+        <v>22.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>178.3846153846154</v>
+        <v>183.9375</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>67.07692307692308</v>
+        <v>66.9375</v>
       </c>
       <c r="AY4" t="n">
-        <v>1959615.384615385</v>
+        <v>2718750</v>
       </c>
       <c r="AZ4" t="n">
-        <v>74.53846153846153</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>242</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>140300000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>249</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>215</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>232</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45527.64583333334</v>
+        <v>45528.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">scatena g 
+          <t xml:space="preserve">mariani m 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio alberto braglia
-  modena </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21092</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10248</v>
-      </c>
+        <v>17102</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M5" t="n">
+        <v>70</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O5" t="n">
+        <v>9</v>
+      </c>
+      <c r="P5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>MBn63swN</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>41</v>
-      </c>
-      <c r="N5" t="n">
-        <v>59</v>
-      </c>
-      <c r="O5" t="n">
-        <v>16</v>
-      </c>
-      <c r="P5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>nZ24J27c</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>77</v>
       </c>
       <c r="X5" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1462,100 +1510,1202 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>183.9090909090909</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4727272.727272728</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5230000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>181.4545454545455</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.409090909090909</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>72.40909090909091</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4209090.909090909</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>76.72727272727273</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>185.12</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3603000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>74</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>302</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>34600000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>303</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>190</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>125</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galipo s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>58</v>
+      </c>
+      <c r="N6" t="n">
+        <v>42</v>
+      </c>
+      <c r="O6" t="n">
+        <v>18</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>17</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>24.14285714285714</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>181.3809523809524</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>64.80952380952381</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1091666.666666667</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>26.23076923076923</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>183.9230769230769</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>65.53846153846153</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>909615.3846153846</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>69.92307692307692</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>63</v>
+      </c>
+      <c r="N7" t="n">
+        <v>37</v>
+      </c>
+      <c r="O7" t="n">
+        <v>16</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>69.54545454545455</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1772727.272727273</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>72.63636363636364</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>24.54166666666667</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>69.04166666666667</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2191666.666666667</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8811</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>34</v>
+      </c>
+      <c r="N8" t="n">
+        <v>66</v>
+      </c>
+      <c r="O8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>67.36363636363636</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1615909.090909091</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>182.6363636363636</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70.09090909090909</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>23.09090909090909</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>182.1818181818182</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>66.40909090909091</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1995454.545454545</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>73.40909090909091</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>24.04545454545455</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>183.1818181818182</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2620454.545454545</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>75.86363636363636</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cosso f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F9" t="n">
+        <v>23061</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>54</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1658333.333333333</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1119000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>24.15789473684211</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>183.5263157894737</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.052631578947368</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>67.36842105263158</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1738157.894736842</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>72.84210526315789</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>65.93333333333334</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1074333.333333333</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massimi l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5017</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>36</v>
+      </c>
+      <c r="N10" t="n">
+        <v>64</v>
+      </c>
+      <c r="O10" t="n">
+        <v>13</v>
+      </c>
+      <c r="P10" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="n">
+        <v>14</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>0M9xNN8N</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>183.4</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1387500</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>182.6</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1470000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>26.95454545454545</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>183.3636363636364</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.272727272727273</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>67.27272727272727</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1215681.818181818</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>70.81818181818181</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>181.7826086956522</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.130434782608696</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>64.73913043478261</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1059347.826086957</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>69.47826086956522</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>22.27272727272727</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>183.7272727272727</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>68.54545454545455</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3325000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>75.90909090909091</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>22.16666666666667</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>183.9444444444445</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>66.22222222222223</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1955555.555555556</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>76.72222222222223</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>180.1111111111111</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1672222.222222222</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>72.44444444444444</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pezzuto i 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto picco
+  la spezia </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>11466</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>52</v>
+      </c>
+      <c r="N11" t="n">
+        <v>48</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>19</v>
+      </c>
+      <c r="T11" t="n">
+        <v>18</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>184.8888888888889</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1516666.666666667</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>23.77272727272727</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>184.3181818181818</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>65.04545454545455</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1237500</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>71.54545454545455</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>22.23809523809524</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>183.8571428571429</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>64.47619047619048</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1373809.523809524</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>73.57142857142857</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN11"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,82 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">giua a 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio artemio franchi
-  florence </t>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43147</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>39211</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29575</v>
+      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.1</v>
+        <v>0.42</v>
       </c>
       <c r="L2" t="n">
-        <v>0.43</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
         <v>8</v>
       </c>
-      <c r="R2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S2" t="n">
-        <v>13</v>
-      </c>
       <c r="T2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,210 +856,210 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>25.44444444444444</v>
+        <v>24.77777777777778</v>
       </c>
       <c r="AD2" t="n">
-        <v>185.4444444444445</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.222222222222222</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AF2" t="n">
-        <v>75.66666666666667</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="AG2" t="n">
-        <v>13922222.22222222</v>
+        <v>4955555.555555556</v>
       </c>
       <c r="AH2" t="n">
-        <v>80.33333333333333</v>
+        <v>77.33333333333333</v>
       </c>
       <c r="AI2" t="n">
-        <v>25.63636363636364</v>
+        <v>23.875</v>
       </c>
       <c r="AJ2" t="n">
-        <v>183.0909090909091</v>
+        <v>185.625</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.090909090909091</v>
+        <v>1.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>79.125</v>
       </c>
       <c r="AM2" t="n">
-        <v>2300000</v>
+        <v>30562500</v>
       </c>
       <c r="AN2" t="n">
-        <v>74.63636363636364</v>
+        <v>84</v>
       </c>
       <c r="AO2" t="n">
-        <v>23.60869565217391</v>
+        <v>25.5625</v>
       </c>
       <c r="AP2" t="n">
-        <v>182.0869565217391</v>
+        <v>183.1875</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.347826086956522</v>
+        <v>1.0625</v>
       </c>
       <c r="AR2" t="n">
-        <v>74.21739130434783</v>
+        <v>70.3125</v>
       </c>
       <c r="AS2" t="n">
-        <v>11895652.17391304</v>
+        <v>2892187.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>80.56521739130434</v>
+        <v>74.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.52173913043478</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="AV2" t="n">
-        <v>184.1304347826087</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>66.47826086956522</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="AY2" t="n">
-        <v>1631304.347826087</v>
+        <v>11708333.33333333</v>
       </c>
       <c r="AZ2" t="n">
-        <v>73.65217391304348</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="BA2" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>185.5</v>
+        <v>185</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BD2" t="n">
         <v>2</v>
       </c>
       <c r="BE2" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="BF2" t="n">
-        <v>30500000</v>
+        <v>7900000</v>
       </c>
       <c r="BG2" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="BH2" t="n">
-        <v>26.75</v>
+        <v>28</v>
       </c>
       <c r="BI2" t="n">
-        <v>178.75</v>
+        <v>185.75</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK2" t="n">
         <v>4</v>
       </c>
       <c r="BL2" t="n">
-        <v>284</v>
+        <v>320</v>
       </c>
       <c r="BM2" t="n">
-        <v>14625000</v>
+        <v>96000000</v>
       </c>
       <c r="BN2" t="n">
-        <v>299</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28177</v>
+        <v>16416</v>
       </c>
       <c r="F3" t="n">
-        <v>20451</v>
+        <v>16365</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.65</v>
+        <v>1.12</v>
       </c>
       <c r="L3" t="n">
-        <v>3.51</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="O3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P3" t="n">
         <v>13</v>
       </c>
-      <c r="P3" t="n">
-        <v>24</v>
-      </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1074,208 +1076,210 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="AC3" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>185.7272727272727</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4990909.090909091</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>76.36363636363636</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>73.125</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="AO3" t="n">
         <v>26.88888888888889</v>
       </c>
-      <c r="AD3" t="n">
-        <v>185.7777777777778</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>75.44444444444444</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10711111.11111111</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>77.66666666666667</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>188</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>23.29411764705882</v>
-      </c>
       <c r="AP3" t="n">
-        <v>184</v>
+        <v>184.6296296296296</v>
       </c>
       <c r="AQ3" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>69.85185185185185</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2369444.444444444</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>73.81481481481481</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>186.8571428571429</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>70.71428571428571</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3926071.428571429</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>175</v>
+      </c>
+      <c r="BC3" t="n">
         <v>1</v>
       </c>
-      <c r="AR3" t="n">
-        <v>70.41176470588235</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5413235.294117647</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>76.23529411764706</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>188.1111111111111</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="BD3" t="n">
         <v>1</v>
       </c>
-      <c r="AX3" t="n">
-        <v>73.44444444444444</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10795555.55555556</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>79.11111111111111</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>22.33333333333333</v>
-      </c>
-      <c r="BB3" t="n">
+      <c r="BE3" t="n">
+        <v>67</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI3" t="n">
         <v>187</v>
       </c>
-      <c r="BC3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>220</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>47500000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>244</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>189.25</v>
-      </c>
       <c r="BJ3" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BL3" t="n">
-        <v>314</v>
+        <v>142</v>
       </c>
       <c r="BM3" t="n">
-        <v>74000000</v>
+        <v>4200000</v>
       </c>
       <c r="BN3" t="n">
-        <v>329</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">zufferli l 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>80018</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>70634</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67517</v>
+      </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.14</v>
+        <v>2.98</v>
       </c>
       <c r="L4" t="n">
-        <v>0.38</v>
+        <v>2.87</v>
       </c>
       <c r="M4" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="N4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="O4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
         <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1292,208 +1296,196 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>29.2</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="AD4" t="n">
-        <v>182.7</v>
+        <v>181.6666666666667</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="AF4" t="n">
-        <v>83.59999999999999</v>
+        <v>79.22222222222223</v>
       </c>
       <c r="AG4" t="n">
-        <v>38100000</v>
+        <v>24755555.55555556</v>
       </c>
       <c r="AH4" t="n">
-        <v>84.8</v>
+        <v>81.11111111111111</v>
       </c>
       <c r="AI4" t="n">
-        <v>23.77777777777778</v>
+        <v>24.09090909090909</v>
       </c>
       <c r="AJ4" t="n">
-        <v>180.7777777777778</v>
+        <v>184.8181818181818</v>
       </c>
       <c r="AK4" t="n">
         <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>71.88888888888889</v>
+        <v>71.18181818181819</v>
       </c>
       <c r="AM4" t="n">
-        <v>5477777.777777778</v>
+        <v>3327272.727272727</v>
       </c>
       <c r="AN4" t="n">
-        <v>78.11111111111111</v>
+        <v>76.72727272727273</v>
       </c>
       <c r="AO4" t="n">
-        <v>26.07692307692308</v>
+        <v>23.94736842105263</v>
       </c>
       <c r="AP4" t="n">
-        <v>184.2692307692308</v>
+        <v>180.3684210526316</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.807692307692308</v>
+        <v>1.473684210526316</v>
       </c>
       <c r="AR4" t="n">
-        <v>78.76923076923077</v>
+        <v>74.73684210526316</v>
       </c>
       <c r="AS4" t="n">
-        <v>23684615.38461538</v>
+        <v>12918421.05263158</v>
       </c>
       <c r="AT4" t="n">
-        <v>81.84615384615384</v>
+        <v>80.36842105263158</v>
       </c>
       <c r="AU4" t="n">
-        <v>22.5</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="AV4" t="n">
-        <v>183.9375</v>
+        <v>181.9583333333333</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>66.9375</v>
+        <v>68</v>
       </c>
       <c r="AY4" t="n">
-        <v>2718750</v>
+        <v>2771458.333333333</v>
       </c>
       <c r="AZ4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>182</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>242</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>140300000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>249</v>
-      </c>
+        <v>75.04166666666667</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>24.33333333333333</v>
+        <v>25.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>182</v>
+        <v>187.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BK4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="BM4" t="n">
-        <v>11100000</v>
+        <v>11825000</v>
       </c>
       <c r="BN4" t="n">
-        <v>232</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17102</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>54726</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45000</v>
+      </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.36</v>
+        <v>1.92</v>
       </c>
       <c r="L5" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>11</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
       </c>
       <c r="T5" t="n">
         <v>17</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1510,204 +1502,192 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>25.63636363636364</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AD5" t="n">
-        <v>183.9090909090909</v>
+        <v>181.9090909090909</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.454545454545455</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="AF5" t="n">
-        <v>72.27272727272727</v>
+        <v>80.45454545454545</v>
       </c>
       <c r="AG5" t="n">
-        <v>4727272.727272728</v>
+        <v>31700000</v>
       </c>
       <c r="AH5" t="n">
-        <v>76.54545454545455</v>
+        <v>82.18181818181819</v>
       </c>
       <c r="AI5" t="n">
-        <v>26.7</v>
+        <v>25.81818181818182</v>
       </c>
       <c r="AJ5" t="n">
-        <v>184.3</v>
+        <v>185.9090909090909</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>75.54545454545455</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>8472727.272727273</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>78.45454545454545</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>181.8666666666667</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10781666.66666667</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>77.86666666666666</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>185.68</v>
+      </c>
+      <c r="AW5" t="n">
         <v>1.2</v>
       </c>
-      <c r="AL5" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>5230000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>181.4545454545455</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.409090909090909</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>72.40909090909091</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4209090.909090909</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>76.72727272727273</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>185.12</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AX5" t="n">
-        <v>70.8</v>
+        <v>71.84</v>
       </c>
       <c r="AY5" t="n">
-        <v>3603000</v>
+        <v>5754000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>74</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>302</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>34600000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>303</v>
-      </c>
+        <v>78.08</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>19.5</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="BI5" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="BJ5" t="n">
         <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL5" t="n">
-        <v>125</v>
+        <v>216</v>
       </c>
       <c r="BM5" t="n">
-        <v>2250000</v>
+        <v>29400000</v>
       </c>
       <c r="BN5" t="n">
-        <v>153</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45529.64583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">galipo s 
+          <t xml:space="preserve">rutella d 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio mario rigamonti
-  brescia </t>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19500</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>14650</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11788</v>
+      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>jci0qO9B</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
+          <t>hKSfjtsQ</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>lb1XFX3n</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1724,31 +1704,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>25.5</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AD6" t="n">
-        <v>184.7</v>
+        <v>180.4444444444445</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>66.40000000000001</v>
+        <v>66.88888888888889</v>
       </c>
       <c r="AG6" t="n">
-        <v>1225000</v>
+        <v>1030555.555555556</v>
       </c>
       <c r="AH6" t="n">
-        <v>70.09999999999999</v>
+        <v>69.22222222222223</v>
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
@@ -1757,41 +1733,29 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>24.14285714285714</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AP6" t="n">
-        <v>181.3809523809524</v>
+        <v>184.2857142857143</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>64.80952380952381</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="AS6" t="n">
-        <v>1091666.666666667</v>
+        <v>1171428.571428571</v>
       </c>
       <c r="AT6" t="n">
-        <v>71.66666666666667</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>26.23076923076923</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>183.9230769230769</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>65.53846153846153</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>909615.3846153846</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>69.92307692307692</v>
-      </c>
+        <v>70.57142857142857</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -1810,78 +1774,80 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45529.64583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ghersini d 
+          <t xml:space="preserve">crezzini v 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giovanni zini
-  cremona </t>
+          <t xml:space="preserve">stadio danilo martelli
+  mantova </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20641</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>5423</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8262</v>
+      </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>KUzfp5N3</t>
+          <t>z7WK5Pwb</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>p84TeBhA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="P7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
         <v>10</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3</v>
-      </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="T7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>hrkecaMB</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>lSb6U6l0</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1896,71 +1862,71 @@
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
-        <v>26.18181818181818</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>184.3636363636364</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1</v>
       </c>
-      <c r="AF7" t="n">
-        <v>69.54545454545455</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1772727.272727273</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>72.63636363636364</v>
-      </c>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1317500</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>72.09999999999999</v>
+      </c>
       <c r="AO7" t="n">
-        <v>24.54166666666667</v>
+        <v>30.14285714285714</v>
       </c>
       <c r="AP7" t="n">
-        <v>183.3333333333333</v>
+        <v>183.4285714285714</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>69.04166666666667</v>
+        <v>68.14285714285714</v>
       </c>
       <c r="AS7" t="n">
-        <v>2191666.666666667</v>
+        <v>1157142.857142857</v>
       </c>
       <c r="AT7" t="n">
-        <v>74.375</v>
+        <v>68.14285714285714</v>
       </c>
       <c r="AU7" t="n">
-        <v>21.8</v>
+        <v>23.21428571428572</v>
       </c>
       <c r="AV7" t="n">
-        <v>180.8</v>
+        <v>183.4285714285714</v>
       </c>
       <c r="AW7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>64.40000000000001</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="AY7" t="n">
-        <v>1350000</v>
+        <v>1000000</v>
       </c>
       <c r="AZ7" t="n">
-        <v>74.59999999999999</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1977,736 +1943,6 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
-  pisa </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>14869</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8811</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>roasMsOT</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>n38Nktmn</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>34</v>
-      </c>
-      <c r="N8" t="n">
-        <v>66</v>
-      </c>
-      <c r="O8" t="n">
-        <v>11</v>
-      </c>
-      <c r="P8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>20</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>GfucctAF</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Wn0poKgt</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>77</v>
-      </c>
-      <c r="X8" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="AC8" t="n">
-        <v>24.81818181818182</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>186</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>67.36363636363636</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1615909.090909091</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>72</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>182.6363636363636</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>70.09090909090909</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>23.09090909090909</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>182.1818181818182</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>66.40909090909091</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1995454.545454545</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>73.40909090909091</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>24.04545454545455</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>183.1818181818182</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.045454545454545</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>2620454.545454545</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>75.86363636363636</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cosso f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F9" t="n">
-        <v>23061</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>6ulJbMCe</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>54</v>
-      </c>
-      <c r="N9" t="n">
-        <v>46</v>
-      </c>
-      <c r="O9" t="n">
-        <v>9</v>
-      </c>
-      <c r="P9" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>11</v>
-      </c>
-      <c r="T9" t="n">
-        <v>12</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>2kfSDavF</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>77</v>
-      </c>
-      <c r="X9" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>181.5555555555555</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>69</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1658333.333333333</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>73.33333333333333</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1119000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>24.15789473684211</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>183.5263157894737</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.052631578947368</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>67.36842105263158</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1738157.894736842</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>72.84210526315789</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>65.93333333333334</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1074333.333333333</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massimi l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>21525</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5017</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>QDdvI0zl</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>xddf1qfh</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>36</v>
-      </c>
-      <c r="N10" t="n">
-        <v>64</v>
-      </c>
-      <c r="O10" t="n">
-        <v>13</v>
-      </c>
-      <c r="P10" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="n">
-        <v>14</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>77</v>
-      </c>
-      <c r="X10" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
-        <v>22.27272727272727</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>183.7272727272727</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>68.54545454545455</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3325000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>75.90909090909091</v>
-      </c>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
-        <v>22.16666666666667</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>183.9444444444445</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>66.22222222222223</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1955555.555555556</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>76.72222222222223</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>23.77777777777778</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>180.1111111111111</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>67.11111111111111</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1672222.222222222</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>72.44444444444444</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pezzuto i 
-  ita </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio alberto picco
-  la spezia </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>11466</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>re6VD39b</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>52</v>
-      </c>
-      <c r="N11" t="n">
-        <v>48</v>
-      </c>
-      <c r="O11" t="n">
-        <v>12</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>19</v>
-      </c>
-      <c r="T11" t="n">
-        <v>18</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>O6SinSSs</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
-        <v>77</v>
-      </c>
-      <c r="X11" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AC11" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>184.8888888888889</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>67.66666666666667</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1516666.666666667</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>71.77777777777777</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>22.44444444444444</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>185.1111111111111</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>66.11111111111111</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1619444.444444444</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>73.77777777777777</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>23.77272727272727</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>184.3181818181818</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>65.04545454545455</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1237500</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>71.54545454545455</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>22.23809523809524</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>183.8571428571429</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>64.47619047619048</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1373809.523809524</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>73.57142857142857</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,84 +762,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.65625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">giua a 
+          <t xml:space="preserve">marchetti m 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>39211</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29575</v>
-      </c>
+        <v>80018</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.42</v>
+        <v>1.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="M2" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N2" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -856,210 +854,208 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>24.77777777777778</v>
+        <v>28.81818181818182</v>
       </c>
       <c r="AD2" t="n">
-        <v>183.6666666666667</v>
+        <v>181.9090909090909</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.111111111111111</v>
+        <v>2.636363636363636</v>
       </c>
       <c r="AF2" t="n">
-        <v>72.66666666666667</v>
+        <v>84</v>
       </c>
       <c r="AG2" t="n">
-        <v>4955555.555555556</v>
+        <v>45181818.18181818</v>
       </c>
       <c r="AH2" t="n">
-        <v>77.33333333333333</v>
+        <v>85.27272727272727</v>
       </c>
       <c r="AI2" t="n">
-        <v>23.875</v>
+        <v>25.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>185.625</v>
+        <v>186.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>79.125</v>
+        <v>76.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>30562500</v>
+        <v>13650000</v>
       </c>
       <c r="AN2" t="n">
-        <v>84</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>25.5625</v>
+        <v>26.08333333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>183.1875</v>
+        <v>184.4166666666667</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.0625</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AR2" t="n">
-        <v>70.3125</v>
+        <v>79.58333333333333</v>
       </c>
       <c r="AS2" t="n">
-        <v>2892187.5</v>
+        <v>29945833.33333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>74.25</v>
+        <v>82.70833333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="AV2" t="n">
-        <v>186.6666666666667</v>
+        <v>186.2307692307692</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.333333333333333</v>
+        <v>1.615384615384615</v>
       </c>
       <c r="AX2" t="n">
-        <v>75.83333333333333</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="AY2" t="n">
-        <v>11708333.33333333</v>
+        <v>13420000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>78.66666666666667</v>
+        <v>79.53846153846153</v>
       </c>
       <c r="BA2" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
-        <v>141</v>
+        <v>72</v>
       </c>
       <c r="BF2" t="n">
-        <v>7900000</v>
+        <v>3300000</v>
       </c>
       <c r="BG2" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="BH2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BI2" t="n">
-        <v>185.75</v>
+        <v>189.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="BM2" t="n">
-        <v>96000000</v>
+        <v>81300000</v>
       </c>
       <c r="BN2" t="n">
-        <v>325</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45530.5625</v>
+        <v>45534.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">di bello m 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio pierluigi penzo
+  venice </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16416</v>
-      </c>
-      <c r="F3" t="n">
-        <v>16365</v>
-      </c>
+        <v>11150</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>0.88</v>
       </c>
       <c r="M3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N3" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="O3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1076,217 +1072,213 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AC3" t="n">
         <v>25.09090909090909</v>
       </c>
       <c r="AD3" t="n">
-        <v>185.7272727272727</v>
+        <v>184.9090909090909</v>
       </c>
       <c r="AE3" t="n">
         <v>1.090909090909091</v>
       </c>
       <c r="AF3" t="n">
-        <v>72.72727272727273</v>
+        <v>70.09090909090909</v>
       </c>
       <c r="AG3" t="n">
-        <v>4990909.090909091</v>
+        <v>2709090.909090909</v>
       </c>
       <c r="AH3" t="n">
-        <v>76.36363636363636</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="n">
-        <v>25.375</v>
+        <v>26.625</v>
       </c>
       <c r="AJ3" t="n">
-        <v>181.25</v>
+        <v>186.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.25</v>
+        <v>1.375</v>
       </c>
       <c r="AL3" t="n">
-        <v>73.125</v>
+        <v>75.375</v>
       </c>
       <c r="AM3" t="n">
-        <v>5650000</v>
+        <v>11237500</v>
       </c>
       <c r="AN3" t="n">
-        <v>75.875</v>
+        <v>77.875</v>
       </c>
       <c r="AO3" t="n">
-        <v>26.88888888888889</v>
+        <v>25.21052631578947</v>
       </c>
       <c r="AP3" t="n">
-        <v>184.6296296296296</v>
+        <v>184.2631578947368</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>69.85185185185185</v>
+        <v>68.05263157894737</v>
       </c>
       <c r="AS3" t="n">
-        <v>2369444.444444444</v>
+        <v>1943157.894736842</v>
       </c>
       <c r="AT3" t="n">
-        <v>73.81481481481481</v>
+        <v>73.89473684210526</v>
       </c>
       <c r="AU3" t="n">
-        <v>27</v>
+        <v>24.14285714285714</v>
       </c>
       <c r="AV3" t="n">
-        <v>186.8571428571429</v>
+        <v>183.6190476190476</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.142857142857143</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX3" t="n">
-        <v>70.71428571428571</v>
+        <v>71.28571428571429</v>
       </c>
       <c r="AY3" t="n">
-        <v>3926071.428571429</v>
+        <v>5953571.428571428</v>
       </c>
       <c r="AZ3" t="n">
-        <v>72.28571428571429</v>
+        <v>76.38095238095238</v>
       </c>
       <c r="BA3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>175</v>
+        <v>173.5</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE3" t="n">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="BF3" t="n">
-        <v>1400000</v>
+        <v>8100000</v>
       </c>
       <c r="BG3" t="n">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="BH3" t="n">
-        <v>29</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="BI3" t="n">
         <v>187</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.5</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BK3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL3" t="n">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="BM3" t="n">
-        <v>4200000</v>
+        <v>47500000</v>
       </c>
       <c r="BN3" t="n">
-        <v>143</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
+          <t xml:space="preserve">collu g 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70634</v>
+        <v>23860</v>
       </c>
       <c r="F4" t="n">
-        <v>67517</v>
+        <v>11870</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>34</v>
+      </c>
+      <c r="N4" t="n">
+        <v>66</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
         <v>2</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="M4" t="n">
-        <v>73</v>
-      </c>
-      <c r="N4" t="n">
-        <v>27</v>
-      </c>
-      <c r="O4" t="n">
-        <v>26</v>
-      </c>
-      <c r="P4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>77</v>
       </c>
       <c r="X4" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1294,87 +1286,71 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>26.11111111111111</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>181.6666666666667</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.111111111111111</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>79.22222222222223</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>24755555.55555556</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>81.11111111111111</v>
-      </c>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>24.09090909090909</v>
+        <v>25.88888888888889</v>
       </c>
       <c r="AJ4" t="n">
-        <v>184.8181818181818</v>
+        <v>182.2222222222222</v>
       </c>
       <c r="AK4" t="n">
         <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>71.18181818181819</v>
+        <v>66.55555555555556</v>
       </c>
       <c r="AM4" t="n">
-        <v>3327272.727272727</v>
+        <v>1175000</v>
       </c>
       <c r="AN4" t="n">
-        <v>76.72727272727273</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="AO4" t="n">
-        <v>23.94736842105263</v>
+        <v>23.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>180.3684210526316</v>
+        <v>178.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.473684210526316</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>74.73684210526316</v>
+        <v>66.625</v>
       </c>
       <c r="AS4" t="n">
-        <v>12918421.05263158</v>
+        <v>1443750</v>
       </c>
       <c r="AT4" t="n">
-        <v>80.36842105263158</v>
+        <v>71.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>22.66666666666667</v>
+        <v>25.4375</v>
       </c>
       <c r="AV4" t="n">
-        <v>181.9583333333333</v>
+        <v>183.1875</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>68</v>
+        <v>66.0625</v>
       </c>
       <c r="AY4" t="n">
-        <v>2771458.333333333</v>
+        <v>1164062.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>75.04166666666667</v>
+        <v>69.6875</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
@@ -1383,116 +1359,98 @@
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>187.4</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>347</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>11825000</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>363</v>
-      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">di marco d 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54726</v>
+        <v>20987</v>
       </c>
       <c r="F5" t="n">
-        <v>45000</v>
+        <v>8006</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>p84TeBhA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.46</v>
-      </c>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
+        <v>61</v>
+      </c>
+      <c r="N5" t="n">
         <v>39</v>
       </c>
-      <c r="N5" t="n">
-        <v>61</v>
-      </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>O6SinSSs</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>77</v>
       </c>
       <c r="X5" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1502,85 +1460,85 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>26.27272727272727</v>
+        <v>25.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>181.9090909090909</v>
+        <v>184.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.545454545454545</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>80.45454545454545</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>31700000</v>
+        <v>1215000</v>
       </c>
       <c r="AH5" t="n">
-        <v>82.18181818181819</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AI5" t="n">
-        <v>25.81818181818182</v>
+        <v>23.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>185.9090909090909</v>
+        <v>185.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.363636363636364</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>75.54545454545455</v>
+        <v>66.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>8472727.272727273</v>
+        <v>1495000</v>
       </c>
       <c r="AN5" t="n">
-        <v>78.45454545454545</v>
+        <v>72.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>26.2</v>
+        <v>22.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>181.8666666666667</v>
+        <v>180.8333333333333</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.733333333333333</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>75.59999999999999</v>
+        <v>63.83333333333334</v>
       </c>
       <c r="AS5" t="n">
-        <v>10781666.66666667</v>
+        <v>1116666.666666667</v>
       </c>
       <c r="AT5" t="n">
-        <v>77.86666666666666</v>
+        <v>72.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>23.44</v>
+        <v>25.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>185.68</v>
+        <v>183.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>71.84</v>
+        <v>65.95</v>
       </c>
       <c r="AY5" t="n">
-        <v>5754000</v>
+        <v>1251250</v>
       </c>
       <c r="AZ5" t="n">
-        <v>78.08</v>
+        <v>71.25</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1589,105 +1547,91 @@
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="n">
-        <v>22.33333333333333</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>181</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>216</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>29400000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>237</v>
-      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCxNBHy3</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45529.64583333334</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">rutella d 
+          <t xml:space="preserve">perri m 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio nicola ceravolo
-  catanzaro </t>
+          <t xml:space="preserve">stadio leonardo garilli
+  piacenza </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14650</v>
+        <v>21668</v>
       </c>
       <c r="F6" t="n">
-        <v>11788</v>
+        <v>1480</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
+          <t>hKSfjtsQ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>z7WK5Pwb</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="N6" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>nsYMfLJM</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>tvh4IkLf</t>
+          <t>hrkecaMB</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1702,60 +1646,44 @@
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>p84TeBhA</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>27.77777777777778</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>180.4444444444445</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>66.88888888888889</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1030555.555555556</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>69.22222222222223</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>184.2857142857143</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>65.71428571428571</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1171428.571428571</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>70.57142857142857</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>70.2</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -1774,80 +1702,80 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvdW7ZzS</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45529.64583333334</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">crezzini v 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio danilo martelli
-  mantova </t>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5423</v>
+        <v>58270</v>
       </c>
       <c r="F7" t="n">
-        <v>8262</v>
+        <v>15733</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>z7WK5Pwb</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N7" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="O7" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>hrkecaMB</t>
+          <t>nZ24J27c</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Yika9O16</t>
+          <t>bPHSQi9q</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1862,71 +1790,87 @@
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>68.45454545454545</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1509090.909090909</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>71.09090909090909</v>
+      </c>
       <c r="AI7" t="n">
-        <v>24.4</v>
+        <v>22.9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>183.7</v>
+        <v>186.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>66.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>1317500</v>
+        <v>3562500</v>
       </c>
       <c r="AN7" t="n">
-        <v>72.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AO7" t="n">
-        <v>30.14285714285714</v>
+        <v>25.73913043478261</v>
       </c>
       <c r="AP7" t="n">
-        <v>183.4285714285714</v>
+        <v>177.9565217391304</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>68.14285714285714</v>
+        <v>64.52173913043478</v>
       </c>
       <c r="AS7" t="n">
-        <v>1157142.857142857</v>
+        <v>996304.3478260869</v>
       </c>
       <c r="AT7" t="n">
-        <v>68.14285714285714</v>
+        <v>69.1304347826087</v>
       </c>
       <c r="AU7" t="n">
-        <v>23.21428571428572</v>
+        <v>22.85</v>
       </c>
       <c r="AV7" t="n">
-        <v>183.4285714285714</v>
+        <v>183.45</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AX7" t="n">
-        <v>64.28571428571429</v>
+        <v>66.95</v>
       </c>
       <c r="AY7" t="n">
-        <v>1000000</v>
+        <v>1935000</v>
       </c>
       <c r="AZ7" t="n">
-        <v>71.42857142857143</v>
+        <v>74.25</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1943,6 +1887,1102 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monaldi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1987</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>50</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>16</v>
+      </c>
+      <c r="T8" t="n">
+        <v>13</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>903500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>62.16666666666666</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>929166.6666666666</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1346250</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio pier cesare tombolato
+  cittadella </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7623</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3685</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>52</v>
+      </c>
+      <c r="N9" t="n">
+        <v>48</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>14</v>
+      </c>
+      <c r="T9" t="n">
+        <v>18</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>66</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1790000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>25.23809523809524</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>181.952380952381</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1007142.857142857</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>70.38095238095238</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>24.29166666666667</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>67.04166666666667</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1760416.666666667</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>71.58333333333333</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9394</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>64</v>
+      </c>
+      <c r="N10" t="n">
+        <v>36</v>
+      </c>
+      <c r="O10" t="n">
+        <v>18</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>14</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2380000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>74</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2818181.818181818</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>183.12</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1972000</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>181.4285714285714</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>69.95238095238095</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2583333.333333333</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>74.0952380952381</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9841</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>48</v>
+      </c>
+      <c r="N11" t="n">
+        <v>52</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>16</v>
+      </c>
+      <c r="T11" t="n">
+        <v>13</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>185.1111111111111</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1619444.444444444</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1590000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>21.82608695652174</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>185.0434782608696</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>64.1304347826087</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1358695.652173913</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>25.91304347826087</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>181.5652173913043</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>65.30434782608695</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1058695.652173913</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>69.47826086956522</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9252</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>39</v>
+      </c>
+      <c r="N12" t="n">
+        <v>61</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16</v>
+      </c>
+      <c r="T12" t="n">
+        <v>14</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>77</v>
+      </c>
+      <c r="X12" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1063888.888888889</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>69.22222222222223</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>25.68421052631579</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>181.7894736842105</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>63.89473684210526</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1174736.842105263</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>68.42105263157895</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>24.19047619047619</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>182.7142857142857</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>64.76190476190476</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1086904.761904762</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>71.47619047619048</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15683</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>58</v>
+      </c>
+      <c r="N13" t="n">
+        <v>42</v>
+      </c>
+      <c r="O13" t="n">
+        <v>24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>77</v>
+      </c>
+      <c r="X13" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2131250</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>183.8888888888889</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>22.15384615384615</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>178.6153846153846</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>65.76923076923077</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1940384.615384615</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>75.53846153846153</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>67.08333333333333</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1406041.666666667</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN13"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,82 +762,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">marchetti m 
+          <t xml:space="preserve">massa d 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80018</v>
+        <v>70634</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M2" t="n">
+        <v>47</v>
+      </c>
+      <c r="N2" t="n">
+        <v>53</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="M2" t="n">
-        <v>54</v>
-      </c>
-      <c r="N2" t="n">
-        <v>46</v>
-      </c>
-      <c r="O2" t="n">
-        <v>13</v>
-      </c>
-      <c r="P2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" t="n">
         <v>5</v>
       </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>15</v>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,208 +854,210 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>28.81818181818182</v>
+        <v>25.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>181.9090909090909</v>
+        <v>181.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.636363636363636</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>84</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>45181818.18181818</v>
+        <v>20590000</v>
       </c>
       <c r="AH2" t="n">
-        <v>85.27272727272727</v>
+        <v>81.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>25.5</v>
+        <v>24.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>186.9</v>
+        <v>183.375</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.4</v>
+        <v>1.625</v>
       </c>
       <c r="AL2" t="n">
-        <v>76.5</v>
+        <v>80.25</v>
       </c>
       <c r="AM2" t="n">
-        <v>13650000</v>
+        <v>35700000</v>
       </c>
       <c r="AN2" t="n">
-        <v>80.59999999999999</v>
+        <v>84.75</v>
       </c>
       <c r="AO2" t="n">
-        <v>26.08333333333333</v>
+        <v>25.45</v>
       </c>
       <c r="AP2" t="n">
-        <v>184.4166666666667</v>
+        <v>181.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.833333333333333</v>
+        <v>1.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>79.58333333333333</v>
+        <v>74.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>29945833.33333333</v>
+        <v>9992500</v>
       </c>
       <c r="AT2" t="n">
-        <v>82.70833333333333</v>
+        <v>78.45</v>
       </c>
       <c r="AU2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AV2" t="n">
-        <v>186.2307692307692</v>
+        <v>185.2105263157895</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.615384615384615</v>
+        <v>1.684210526315789</v>
       </c>
       <c r="AX2" t="n">
-        <v>76.92307692307692</v>
+        <v>78.78947368421052</v>
       </c>
       <c r="AY2" t="n">
-        <v>13420000</v>
+        <v>37289473.68421052</v>
       </c>
       <c r="AZ2" t="n">
-        <v>79.53846153846153</v>
+        <v>84.10526315789474</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>183</v>
+        <v>181.5</v>
       </c>
       <c r="BC2" t="n">
         <v>1</v>
       </c>
       <c r="BD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE2" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="n">
-        <v>3300000</v>
+        <v>6700000</v>
       </c>
       <c r="BG2" t="n">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="BH2" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>189.6</v>
+        <v>185.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL2" t="n">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="BM2" t="n">
-        <v>81300000</v>
+        <v>89500000</v>
       </c>
       <c r="BN2" t="n">
-        <v>410</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">marcenaro m 
+          <t xml:space="preserve">marinelli l 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pierluigi penzo
-  venice </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11150</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>38279</v>
+      </c>
+      <c r="F3" t="n">
+        <v>25960</v>
+      </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.81</v>
       </c>
       <c r="L3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M3" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="N3" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="O3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1072,188 +1074,192 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>25.09090909090909</v>
+        <v>25.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>184.9090909090909</v>
+        <v>184.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.090909090909091</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>70.09090909090909</v>
+        <v>75.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>2709090.909090909</v>
+        <v>9400000</v>
       </c>
       <c r="AH3" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>24.09090909090909</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>184.8181818181818</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>69.54545454545455</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>2917272.727272727</v>
+      </c>
+      <c r="AN3" t="n">
         <v>75</v>
       </c>
-      <c r="AI3" t="n">
-        <v>26.625</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>186.25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>75.375</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>11237500</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>77.875</v>
-      </c>
       <c r="AO3" t="n">
-        <v>25.21052631578947</v>
+        <v>24.12</v>
       </c>
       <c r="AP3" t="n">
-        <v>184.2631578947368</v>
+        <v>185</v>
       </c>
       <c r="AQ3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>70.76000000000001</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4542000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>22.8695652173913</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>183.9130434782609</v>
+      </c>
+      <c r="AW3" t="n">
         <v>1</v>
       </c>
-      <c r="AR3" t="n">
-        <v>68.05263157894737</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1943157.894736842</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>73.89473684210526</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>24.14285714285714</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>183.6190476190476</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.047619047619048</v>
-      </c>
       <c r="AX3" t="n">
-        <v>71.28571428571429</v>
+        <v>69.60869565217391</v>
       </c>
       <c r="AY3" t="n">
-        <v>5953571.428571428</v>
+        <v>3240217.391304348</v>
       </c>
       <c r="AZ3" t="n">
-        <v>76.38095238095238</v>
+        <v>75.91304347826087</v>
       </c>
       <c r="BA3" t="n">
-        <v>22</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="BB3" t="n">
-        <v>173.5</v>
+        <v>185</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>138</v>
+        <v>442</v>
       </c>
       <c r="BF3" t="n">
-        <v>8100000</v>
+        <v>58400000</v>
       </c>
       <c r="BG3" t="n">
-        <v>153</v>
+        <v>476</v>
       </c>
       <c r="BH3" t="n">
-        <v>22.33333333333333</v>
+        <v>25.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>187</v>
+        <v>187.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.333333333333333</v>
+        <v>1.2</v>
       </c>
       <c r="BK3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
-        <v>220</v>
+        <v>352</v>
       </c>
       <c r="BM3" t="n">
-        <v>47500000</v>
+        <v>16425000</v>
       </c>
       <c r="BN3" t="n">
-        <v>244</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zVpmZBZQ</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45532.64583333334</v>
+        <v>45535.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">collu g 
+          <t xml:space="preserve">fabbri m 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23860</v>
+        <v>40670</v>
       </c>
       <c r="F4" t="n">
-        <v>11870</v>
+        <v>26386</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>xddf1qfh</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
         <v>2</v>
@@ -1262,23 +1268,23 @@
         <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>nsYMfLJM</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>77</v>
       </c>
       <c r="X4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1286,79 +1292,109 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>181.875</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>72.375</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5550000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>77.875</v>
+      </c>
       <c r="AI4" t="n">
-        <v>25.88888888888889</v>
+        <v>25.09090909090909</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182.2222222222222</v>
+        <v>185.7272727272727</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AL4" t="n">
-        <v>66.55555555555556</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="AM4" t="n">
-        <v>1175000</v>
+        <v>4990909.090909091</v>
       </c>
       <c r="AN4" t="n">
-        <v>70.44444444444444</v>
+        <v>76.36363636363636</v>
       </c>
       <c r="AO4" t="n">
-        <v>23.75</v>
+        <v>23.35714285714286</v>
       </c>
       <c r="AP4" t="n">
-        <v>178.75</v>
+        <v>183.6428571428571</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>66.625</v>
+        <v>68.35714285714286</v>
       </c>
       <c r="AS4" t="n">
-        <v>1443750</v>
+        <v>3046428.571428571</v>
       </c>
       <c r="AT4" t="n">
-        <v>71.75</v>
+        <v>74.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>25.4375</v>
+        <v>27.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>183.1875</v>
+        <v>183.3214285714286</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>1.357142857142857</v>
       </c>
       <c r="AX4" t="n">
-        <v>66.0625</v>
+        <v>70.10714285714286</v>
       </c>
       <c r="AY4" t="n">
-        <v>1164062.5</v>
+        <v>2147321.428571429</v>
       </c>
       <c r="AZ4" t="n">
-        <v>69.6875</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
+        <v>73.42857142857143</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>215</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>232</v>
+      </c>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
@@ -1370,80 +1406,78 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SSPRRTR0</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.64583333334</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">cosso f 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio san vito luigi marulla
-  cosenza </t>
+          <t xml:space="preserve">stadio alberto braglia
+  modena </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20987</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8006</v>
-      </c>
+        <v>21092</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
+          <t>MBn63swN</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>re6VD39b</t>
+          <t>C0yUqo8c</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Yika9O16</t>
+          <t>YTZ7S7pk</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>O6SinSSs</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1460,85 +1494,85 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>184.9</v>
+        <v>183.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>66.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>1215000</v>
+        <v>1467500</v>
       </c>
       <c r="AH5" t="n">
-        <v>70.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>23.8</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AJ5" t="n">
-        <v>185.9</v>
+        <v>182.4444444444445</v>
       </c>
       <c r="AK5" t="n">
         <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>66.5</v>
+        <v>66.77777777777777</v>
       </c>
       <c r="AM5" t="n">
-        <v>1495000</v>
+        <v>1100000</v>
       </c>
       <c r="AN5" t="n">
-        <v>72.2</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="AO5" t="n">
-        <v>22.5</v>
+        <v>25.34782608695652</v>
       </c>
       <c r="AP5" t="n">
-        <v>180.8333333333333</v>
+        <v>182.2173913043478</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>1.217391304347826</v>
       </c>
       <c r="AR5" t="n">
-        <v>63.83333333333334</v>
+        <v>65.78260869565217</v>
       </c>
       <c r="AS5" t="n">
-        <v>1116666.666666667</v>
+        <v>1167391.304347826</v>
       </c>
       <c r="AT5" t="n">
-        <v>72.25</v>
+        <v>70.43478260869566</v>
       </c>
       <c r="AU5" t="n">
-        <v>25.5</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="AV5" t="n">
-        <v>183.3</v>
+        <v>181.1818181818182</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>65.95</v>
+        <v>64.81818181818181</v>
       </c>
       <c r="AY5" t="n">
-        <v>1251250</v>
+        <v>1029545.454545455</v>
       </c>
       <c r="AZ5" t="n">
-        <v>71.25</v>
+        <v>70.72727272727273</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1558,80 +1592,78 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>p4dhrkCs</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45532.64583333334</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">perri m 
+          <t xml:space="preserve">galipo s 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio leonardo garilli
-  piacenza </t>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21668</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1480</v>
-      </c>
+        <v>14869</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>roasMsOT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>z7WK5Pwb</t>
+          <t>6ulJbMCe</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>tvh4IkLf</t>
+          <t>GfucctAF</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>hrkecaMB</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1646,43 +1678,83 @@
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>185.3636363636364</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1609090.909090909</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1119000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>24.27272727272727</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>182.9545454545455</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>65.54545454545455</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1394318.181818182</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>71.81818181818181</v>
+      </c>
       <c r="AU6" t="n">
-        <v>29</v>
+        <v>26.57894736842105</v>
       </c>
       <c r="AV6" t="n">
-        <v>181.6</v>
+        <v>181.7368421052632</v>
       </c>
       <c r="AW6" t="n">
         <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>70.2</v>
+        <v>64.73684210526316</v>
       </c>
       <c r="AY6" t="n">
-        <v>1820000</v>
+        <v>979210.5263157894</v>
       </c>
       <c r="AZ6" t="n">
-        <v>70.2</v>
+        <v>68.73684210526316</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
@@ -1702,80 +1774,78 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Y54hDUC7</t>
+          <t>CGH1PgIF</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45531.64583333334</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio san nicola
-  bari </t>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>58270</v>
-      </c>
-      <c r="F7" t="n">
-        <v>15733</v>
-      </c>
+        <v>21525</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>KUzfp5N3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
         <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>nZ24J27c</t>
+          <t>bPHSQi9q</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1792,85 +1862,85 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AD7" t="n">
-        <v>183.0909090909091</v>
+        <v>185.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.090909090909091</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>68.45454545454545</v>
+        <v>69.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1509090.909090909</v>
+        <v>3277500</v>
       </c>
       <c r="AH7" t="n">
-        <v>71.09090909090909</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>22.9</v>
+        <v>25.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>186.4</v>
+        <v>184.2</v>
       </c>
       <c r="AK7" t="n">
         <v>1.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>69.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="AM7" t="n">
-        <v>3562500</v>
+        <v>2210000</v>
       </c>
       <c r="AN7" t="n">
-        <v>76.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="AO7" t="n">
-        <v>25.73913043478261</v>
+        <v>22.63157894736842</v>
       </c>
       <c r="AP7" t="n">
-        <v>177.9565217391304</v>
+        <v>181.8947368421053</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="AR7" t="n">
-        <v>64.52173913043478</v>
+        <v>67.05263157894737</v>
       </c>
       <c r="AS7" t="n">
-        <v>996304.3478260869</v>
+        <v>2115789.47368421</v>
       </c>
       <c r="AT7" t="n">
-        <v>69.1304347826087</v>
+        <v>74.36842105263158</v>
       </c>
       <c r="AU7" t="n">
-        <v>22.85</v>
+        <v>26.52173913043478</v>
       </c>
       <c r="AV7" t="n">
-        <v>183.45</v>
+        <v>182.9565217391304</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.15</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AX7" t="n">
-        <v>66.95</v>
+        <v>69.73913043478261</v>
       </c>
       <c r="AY7" t="n">
-        <v>1935000</v>
+        <v>1930434.782608696</v>
       </c>
       <c r="AZ7" t="n">
-        <v>74.25</v>
+        <v>72.39130434782609</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1890,80 +1960,78 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v3ivyY4E</t>
+          <t>21OYHBAk</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45531.64583333334</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">monaldi m 
+          <t xml:space="preserve">rutella d 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
-  pisa </t>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14869</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1987</v>
-      </c>
+        <v>5539</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>W02MZDnp</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>W02MZDnp</t>
+          <t>jci0qO9B</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N8" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>lSb6U6l0</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>lb1XFX3n</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -1978,71 +2046,87 @@
       <c r="Z8" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1081000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>69.90000000000001</v>
+      </c>
       <c r="AI8" t="n">
-        <v>27.3</v>
+        <v>24.88888888888889</v>
       </c>
       <c r="AJ8" t="n">
-        <v>184.6</v>
+        <v>182.4444444444445</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>66.8</v>
+        <v>67.11111111111111</v>
       </c>
       <c r="AM8" t="n">
-        <v>903500</v>
+        <v>1408333.333333333</v>
       </c>
       <c r="AN8" t="n">
-        <v>70.7</v>
+        <v>71.88888888888889</v>
       </c>
       <c r="AO8" t="n">
-        <v>21.16666666666667</v>
+        <v>23.57142857142857</v>
       </c>
       <c r="AP8" t="n">
-        <v>180</v>
+        <v>184.7142857142857</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>62.16666666666666</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="AS8" t="n">
-        <v>929166.6666666666</v>
+        <v>1263095.238095238</v>
       </c>
       <c r="AT8" t="n">
-        <v>72</v>
+        <v>71.04761904761905</v>
       </c>
       <c r="AU8" t="n">
-        <v>26.7</v>
+        <v>23.41176470588235</v>
       </c>
       <c r="AV8" t="n">
-        <v>181.9</v>
+        <v>181.7058823529412</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>67.05</v>
+        <v>64.17647058823529</v>
       </c>
       <c r="AY8" t="n">
-        <v>1346250</v>
+        <v>1038235.294117647</v>
       </c>
       <c r="AZ8" t="n">
-        <v>70.40000000000001</v>
+        <v>71.11764705882354</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -2062,80 +2146,78 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W0WITkcl</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45531.64583333334</v>
+        <v>45535.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena a 
+          <t xml:space="preserve">maresca f 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pier cesare tombolato
-  cittadella </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7623</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3685</v>
-      </c>
+        <v>36599</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>roasMsOT</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="N9" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="O9" t="n">
         <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="n">
         <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>AZ1NG9tC</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>GfucctAF</t>
+          <t>nZ24J27c</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2152,73 +2234,85 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>71</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1962500</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>72.375</v>
+      </c>
       <c r="AI9" t="n">
-        <v>23.3</v>
+        <v>27.18181818181818</v>
       </c>
       <c r="AJ9" t="n">
+        <v>183</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>67.54545454545455</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1225000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="AP9" t="n">
         <v>183.2</v>
       </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>66</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1790000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>25.23809523809524</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>181.952380952381</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AR9" t="n">
-        <v>65.33333333333333</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>1007142.857142857</v>
+        <v>1456800</v>
       </c>
       <c r="AT9" t="n">
-        <v>70.38095238095238</v>
+        <v>72.84</v>
       </c>
       <c r="AU9" t="n">
-        <v>24.29166666666667</v>
+        <v>25.10526315789474</v>
       </c>
       <c r="AV9" t="n">
-        <v>183.625</v>
+        <v>182.9473684210526</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>67.04166666666667</v>
+        <v>65.10526315789474</v>
       </c>
       <c r="AY9" t="n">
-        <v>1760416.666666667</v>
+        <v>1163947.368421053</v>
       </c>
       <c r="AZ9" t="n">
-        <v>71.58333333333333</v>
+        <v>69.42105263157895</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
@@ -2235,754 +2329,6 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fourneau f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio giovanni zini
-  cremona </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>20641</v>
-      </c>
-      <c r="F10" t="n">
-        <v>9394</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>KUzfp5N3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>n38Nktmn</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>64</v>
-      </c>
-      <c r="N10" t="n">
-        <v>36</v>
-      </c>
-      <c r="O10" t="n">
-        <v>18</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>14</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Wn0poKgt</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>77</v>
-      </c>
-      <c r="X10" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2380000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>74</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>24.27272727272727</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>183.2727272727273</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>70.27272727272727</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>2818181.818181818</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>76.18181818181819</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>24.04</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>183.12</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>68.44</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1972000</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>74</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>181.4285714285714</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>69.95238095238095</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>2583333.333333333</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>74.0952380952381</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio benito stirpe
-  frosinone </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>16227</v>
-      </c>
-      <c r="F11" t="n">
-        <v>9841</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>MBn63swN</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>48</v>
-      </c>
-      <c r="N11" t="n">
-        <v>52</v>
-      </c>
-      <c r="O11" t="n">
-        <v>12</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>16</v>
-      </c>
-      <c r="T11" t="n">
-        <v>13</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>YTZ7S7pk</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
-        <v>77</v>
-      </c>
-      <c r="X11" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AC11" t="n">
-        <v>22.44444444444444</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>185.1111111111111</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>66.11111111111111</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1619444.444444444</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>73.77777777777777</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>183.9</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1590000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>21.82608695652174</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>185.0434782608696</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>64.1304347826087</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1358695.652173913</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>74</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>25.91304347826087</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>181.5652173913043</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.173913043478261</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>65.30434782608695</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1058695.652173913</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>69.47826086956522</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>21525</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9252</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6ulJbMCe</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>jci0qO9B</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>39</v>
-      </c>
-      <c r="N12" t="n">
-        <v>61</v>
-      </c>
-      <c r="O12" t="n">
-        <v>11</v>
-      </c>
-      <c r="P12" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>16</v>
-      </c>
-      <c r="T12" t="n">
-        <v>14</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>lb1XFX3n</t>
-        </is>
-      </c>
-      <c r="W12" t="n">
-        <v>77</v>
-      </c>
-      <c r="X12" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="AC12" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>183.3333333333333</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>66.11111111111111</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1063888.888888889</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>69.22222222222223</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>183.7</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1205000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>25.68421052631579</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>181.7894736842105</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>63.89473684210526</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1174736.842105263</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>68.42105263157895</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>24.19047619047619</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>182.7142857142857</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>64.76190476190476</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1086904.761904762</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>71.47619047619048</v>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feliciani e 
-  ita </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio arechi
-  salerno </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>37800</v>
-      </c>
-      <c r="F13" t="n">
-        <v>15683</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Mq05g4BP</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>58</v>
-      </c>
-      <c r="N13" t="n">
-        <v>42</v>
-      </c>
-      <c r="O13" t="n">
-        <v>24</v>
-      </c>
-      <c r="P13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>15</v>
-      </c>
-      <c r="T13" t="n">
-        <v>9</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>OjWmexQb</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2kfSDavF</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>77</v>
-      </c>
-      <c r="X13" t="n">
-        <v>774</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="AC13" t="n">
-        <v>25.625</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>69.375</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2131250</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>74.125</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>183.8888888888889</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>70.55555555555556</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>73.33333333333333</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>22.15384615384615</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>178.6153846153846</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>65.76923076923077</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1940384.615384615</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>75.53846153846153</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>25.125</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>182.3333333333333</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>67.08333333333333</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1406041.666666667</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>71.875</v>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN9"/>
+  <dimension ref="A1:BN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,82 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
+          <t xml:space="preserve">guida m 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico
-  rome </t>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>70634</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>41507</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41375</v>
+      </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.98</v>
+        <v>0.54</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,210 +856,196 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>25.8</v>
+        <v>23.875</v>
       </c>
       <c r="AD2" t="n">
-        <v>181.4</v>
+        <v>185.625</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>78.40000000000001</v>
+        <v>79.125</v>
       </c>
       <c r="AG2" t="n">
-        <v>20590000</v>
+        <v>30562500</v>
       </c>
       <c r="AH2" t="n">
-        <v>81.3</v>
+        <v>84</v>
       </c>
       <c r="AI2" t="n">
-        <v>24.25</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AJ2" t="n">
-        <v>183.375</v>
+        <v>182</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.625</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AL2" t="n">
-        <v>80.25</v>
+        <v>76.33333333333333</v>
       </c>
       <c r="AM2" t="n">
-        <v>35700000</v>
+        <v>17991666.66666667</v>
       </c>
       <c r="AN2" t="n">
-        <v>84.75</v>
+        <v>80.55555555555556</v>
       </c>
       <c r="AO2" t="n">
-        <v>25.45</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>181.75</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>74.5</v>
+        <v>79.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>9992500</v>
+        <v>26583333.33333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>78.45</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>23</v>
+        <v>24.65</v>
       </c>
       <c r="AV2" t="n">
-        <v>185.2105263157895</v>
+        <v>179.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.684210526315789</v>
+        <v>1.65</v>
       </c>
       <c r="AX2" t="n">
-        <v>78.78947368421052</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AY2" t="n">
-        <v>37289473.68421052</v>
+        <v>21997500</v>
       </c>
       <c r="AZ2" t="n">
-        <v>84.10526315789474</v>
+        <v>81.45</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>181.5</v>
+        <v>185.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>140</v>
+        <v>320</v>
       </c>
       <c r="BF2" t="n">
-        <v>6700000</v>
+        <v>96000000</v>
       </c>
       <c r="BG2" t="n">
-        <v>150</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>315</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>89500000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>328</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">marinelli l 
+          <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38279</v>
+        <v>25144</v>
       </c>
       <c r="F3" t="n">
-        <v>25960</v>
+        <v>7020</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.81</v>
+        <v>0.63</v>
       </c>
       <c r="L3" t="n">
-        <v>0.89</v>
+        <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="O3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1074,210 +1062,198 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>184.7</v>
+        <v>185.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>75.7</v>
+        <v>72.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>9400000</v>
+        <v>3910000</v>
       </c>
       <c r="AH3" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>24.09090909090909</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>184.8181818181818</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>69.54545454545455</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>2917272.727272727</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>75</v>
-      </c>
+        <v>75.5</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>24.12</v>
+        <v>24.77777777777778</v>
       </c>
       <c r="AP3" t="n">
-        <v>185</v>
+        <v>186.8888888888889</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.2</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AR3" t="n">
-        <v>70.76000000000001</v>
+        <v>71.05555555555556</v>
       </c>
       <c r="AS3" t="n">
-        <v>4542000</v>
+        <v>3255555.555555556</v>
       </c>
       <c r="AT3" t="n">
-        <v>77.04000000000001</v>
+        <v>75.55555555555556</v>
       </c>
       <c r="AU3" t="n">
-        <v>22.8695652173913</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AV3" t="n">
-        <v>183.9130434782609</v>
+        <v>181.6666666666667</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>69.60869565217391</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="AY3" t="n">
-        <v>3240217.391304348</v>
+        <v>5085416.666666667</v>
       </c>
       <c r="AZ3" t="n">
-        <v>75.91304347826087</v>
+        <v>72.83333333333333</v>
       </c>
       <c r="BA3" t="n">
-        <v>23.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>185</v>
+        <v>172.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BE3" t="n">
-        <v>442</v>
+        <v>153</v>
       </c>
       <c r="BF3" t="n">
-        <v>58400000</v>
+        <v>21200000</v>
       </c>
       <c r="BG3" t="n">
-        <v>476</v>
+        <v>153</v>
       </c>
       <c r="BH3" t="n">
-        <v>25.8</v>
+        <v>31</v>
       </c>
       <c r="BI3" t="n">
-        <v>187.4</v>
+        <v>182</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>352</v>
+        <v>69</v>
       </c>
       <c r="BM3" t="n">
-        <v>16425000</v>
+        <v>1100000</v>
       </c>
       <c r="BN3" t="n">
-        <v>368</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fabbri m 
+          <t xml:space="preserve">colombo a 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40670</v>
+        <v>43147</v>
       </c>
       <c r="F4" t="n">
-        <v>26386</v>
+        <v>18376</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.25</v>
+        <v>1.31</v>
       </c>
       <c r="L4" t="n">
-        <v>1.75</v>
+        <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="N4" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="O4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="n">
         <v>21</v>
       </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="n">
-        <v>13</v>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1294,158 +1270,178 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>24.125</v>
+        <v>25.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>181.875</v>
+        <v>183.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>72.375</v>
+        <v>75.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>5550000</v>
+        <v>12180000</v>
       </c>
       <c r="AH4" t="n">
-        <v>77.875</v>
+        <v>79.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>25.09090909090909</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>185.7272727272727</v>
+        <v>183.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.090909090909091</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>72.72727272727273</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AM4" t="n">
-        <v>4990909.090909091</v>
+        <v>5430000</v>
       </c>
       <c r="AN4" t="n">
-        <v>76.36363636363636</v>
+        <v>77.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>23.35714285714286</v>
+        <v>23.36</v>
       </c>
       <c r="AP4" t="n">
-        <v>183.6428571428571</v>
+        <v>181.76</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="AR4" t="n">
-        <v>68.35714285714286</v>
+        <v>74.44</v>
       </c>
       <c r="AS4" t="n">
-        <v>3046428.571428571</v>
+        <v>11064000</v>
       </c>
       <c r="AT4" t="n">
-        <v>74.5</v>
+        <v>80.48</v>
       </c>
       <c r="AU4" t="n">
-        <v>27.5</v>
+        <v>27.30434782608696</v>
       </c>
       <c r="AV4" t="n">
-        <v>183.3214285714286</v>
+        <v>183.1304347826087</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.357142857142857</v>
+        <v>1.565217391304348</v>
       </c>
       <c r="AX4" t="n">
-        <v>70.10714285714286</v>
+        <v>72.39130434782609</v>
       </c>
       <c r="AY4" t="n">
-        <v>2147321.428571429</v>
+        <v>3752173.913043478</v>
       </c>
       <c r="AZ4" t="n">
-        <v>73.42857142857143</v>
+        <v>75.95652173913044</v>
       </c>
       <c r="BA4" t="n">
-        <v>24.33333333333333</v>
+        <v>26</v>
       </c>
       <c r="BB4" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BE4" t="n">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="BF4" t="n">
-        <v>11100000</v>
+        <v>21000000</v>
       </c>
       <c r="BG4" t="n">
-        <v>232</v>
-      </c>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>181</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>152</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>16900000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dtLQNtsB</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.64583333334</v>
+        <v>45536.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">ayroldi g 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio alberto braglia
-  modena </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21092</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>36599</v>
+      </c>
+      <c r="F5" t="n">
+        <v>30747</v>
+      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MBn63swN</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.72</v>
+      </c>
       <c r="M5" t="n">
         <v>58</v>
       </c>
@@ -1453,38 +1449,38 @@
         <v>42</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
         <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
         <v>16</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>77</v>
       </c>
       <c r="X5" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1494,126 +1490,156 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>183.8</v>
+        <v>184.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>68.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>1467500</v>
+        <v>5330000</v>
       </c>
       <c r="AH5" t="n">
-        <v>71.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>26.66666666666667</v>
+        <v>24.55555555555556</v>
       </c>
       <c r="AJ5" t="n">
-        <v>182.4444444444445</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AL5" t="n">
-        <v>66.77777777777777</v>
+        <v>72.33333333333333</v>
       </c>
       <c r="AM5" t="n">
-        <v>1100000</v>
+        <v>4600000</v>
       </c>
       <c r="AN5" t="n">
-        <v>69.66666666666667</v>
+        <v>77.11111111111111</v>
       </c>
       <c r="AO5" t="n">
-        <v>25.34782608695652</v>
+        <v>27.42105263157895</v>
       </c>
       <c r="AP5" t="n">
-        <v>182.2173913043478</v>
+        <v>183.5263157894737</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.217391304347826</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="AR5" t="n">
-        <v>65.78260869565217</v>
+        <v>71</v>
       </c>
       <c r="AS5" t="n">
-        <v>1167391.304347826</v>
+        <v>4003947.368421053</v>
       </c>
       <c r="AT5" t="n">
-        <v>70.43478260869566</v>
+        <v>72.94736842105263</v>
       </c>
       <c r="AU5" t="n">
-        <v>24.72727272727273</v>
+        <v>25.28571428571428</v>
       </c>
       <c r="AV5" t="n">
-        <v>181.1818181818182</v>
+        <v>183.5238095238095</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX5" t="n">
-        <v>64.81818181818181</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AY5" t="n">
-        <v>1029545.454545455</v>
+        <v>3660714.285714286</v>
       </c>
       <c r="AZ5" t="n">
-        <v>70.72727272727273</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>75.57142857142857</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>344</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>22750000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>394</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>185</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>141</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Ofy73Ced</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.64583333334</v>
+        <v>45535.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">galipo s 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
-  pisa </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14869</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>54726</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50000</v>
+      </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
@@ -1622,55 +1648,59 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>roasMsOT</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.49</v>
+      </c>
       <c r="M6" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="N6" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>GfucctAF</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>77</v>
       </c>
       <c r="X6" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1680,81 +1710,85 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
       <c r="AC6" t="n">
-        <v>23.90909090909091</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AD6" t="n">
-        <v>185.3636363636364</v>
+        <v>181.9090909090909</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="AF6" t="n">
-        <v>67</v>
+        <v>80.45454545454545</v>
       </c>
       <c r="AG6" t="n">
-        <v>1609090.909090909</v>
+        <v>31700000</v>
       </c>
       <c r="AH6" t="n">
-        <v>72.36363636363636</v>
+        <v>82.18181818181819</v>
       </c>
       <c r="AI6" t="n">
-        <v>25.5</v>
+        <v>21.875</v>
       </c>
       <c r="AJ6" t="n">
-        <v>182.9</v>
+        <v>185.25</v>
       </c>
       <c r="AK6" t="n">
         <v>1</v>
       </c>
       <c r="AL6" t="n">
-        <v>64.5</v>
+        <v>69.375</v>
       </c>
       <c r="AM6" t="n">
-        <v>1119000</v>
+        <v>3750000</v>
       </c>
       <c r="AN6" t="n">
-        <v>68.8</v>
+        <v>78.125</v>
       </c>
       <c r="AO6" t="n">
-        <v>24.27272727272727</v>
+        <v>27.05882352941176</v>
       </c>
       <c r="AP6" t="n">
-        <v>182.9545454545455</v>
+        <v>183.7058823529412</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>2.176470588235294</v>
       </c>
       <c r="AR6" t="n">
-        <v>65.54545454545455</v>
+        <v>77.47058823529412</v>
       </c>
       <c r="AS6" t="n">
-        <v>1394318.181818182</v>
+        <v>16913235.29411765</v>
       </c>
       <c r="AT6" t="n">
-        <v>71.81818181818181</v>
+        <v>79</v>
       </c>
       <c r="AU6" t="n">
-        <v>26.57894736842105</v>
+        <v>23.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>181.7368421052632</v>
+        <v>183.52</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AX6" t="n">
-        <v>64.73684210526316</v>
+        <v>68.08</v>
       </c>
       <c r="AY6" t="n">
-        <v>979210.5263157894</v>
+        <v>2602600</v>
       </c>
       <c r="AZ6" t="n">
-        <v>68.73684210526316</v>
+        <v>75.12</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
@@ -1763,89 +1797,105 @@
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BH6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>146</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CGH1PgIF</t>
+          <t>v5l07LdU</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.64583333334</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">perenzoni d 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21525</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>14650</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9348</v>
+      </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>KUzfp5N3</t>
+          <t>hG4fg4z3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>13</v>
+      </c>
+      <c r="T7" t="n">
         <v>11</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>10</v>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>lSb6U6l0</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1862,85 +1912,69 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>23</v>
+        <v>27.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>185.4</v>
+        <v>181</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>69.2</v>
+        <v>66.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>3277500</v>
+        <v>1057500</v>
       </c>
       <c r="AH7" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>184.2</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>2210000</v>
-      </c>
-      <c r="AN7" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>25.13636363636364</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>183.6818181818182</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>66.63636363636364</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1277272.727272727</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>181.0833333333333</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1143750</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>74</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>22.63157894736842</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>181.8947368421053</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.157894736842105</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>67.05263157894737</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2115789.47368421</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>74.36842105263158</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>26.52173913043478</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>182.9565217391304</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.043478260869565</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>69.73913043478261</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1930434.782608696</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>72.39130434782609</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1960,78 +1994,80 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>21OYHBAk</t>
+          <t>fHO9ROsn</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.64583333334</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rutella d 
+          <t xml:space="preserve">bonacina k 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marco druso
-  bolzano </t>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5539</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>16227</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10755</v>
+      </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>W02MZDnp</t>
+          <t>pfo9H1Wp</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>jci0qO9B</t>
+          <t>hKSfjtsQ</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="N8" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
+        <v>23</v>
+      </c>
+      <c r="T8" t="n">
         <v>13</v>
       </c>
-      <c r="T8" t="n">
-        <v>15</v>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>lb1XFX3n</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -2048,85 +2084,69 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>28.9</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="AD8" t="n">
-        <v>183.5</v>
+        <v>184.7777777777778</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>67.90000000000001</v>
+        <v>66.11111111111111</v>
       </c>
       <c r="AG8" t="n">
-        <v>1081000</v>
+        <v>1561111.111111111</v>
       </c>
       <c r="AH8" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>24.88888888888889</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>182.4444444444445</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>67.11111111111111</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1408333.333333333</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>71.88888888888889</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>23.57142857142857</v>
+        <v>23.22727272727273</v>
       </c>
       <c r="AP8" t="n">
-        <v>184.7142857142857</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>65.33333333333333</v>
+        <v>67.31818181818181</v>
       </c>
       <c r="AS8" t="n">
-        <v>1263095.238095238</v>
+        <v>1904545.454545455</v>
       </c>
       <c r="AT8" t="n">
-        <v>71.04761904761905</v>
+        <v>74.36363636363636</v>
       </c>
       <c r="AU8" t="n">
-        <v>23.41176470588235</v>
+        <v>21</v>
       </c>
       <c r="AV8" t="n">
-        <v>181.7058823529412</v>
+        <v>186.4</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>64.17647058823529</v>
+        <v>63.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>1038235.294117647</v>
+        <v>1040000</v>
       </c>
       <c r="AZ8" t="n">
-        <v>71.11764705882354</v>
+        <v>72</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -2146,78 +2166,80 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>v3JgRFm3</t>
+          <t>jqIIP2Cb</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.54166666666</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">maresca f 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio danilo martelli
+  mantova </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>5423</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8651</v>
+      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>z7WK5Pwb</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>Mq05g4BP</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="N9" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="O9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>AZ1NG9tC</t>
+          <t>hrkecaMB</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>nZ24J27c</t>
+          <t>OjWmexQb</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2232,87 +2254,59 @@
       <c r="Z9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="AC9" t="n">
-        <v>28.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>183.375</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>71</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1962500</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>72.375</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>27.18181818181818</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>183</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.090909090909091</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>67.54545454545455</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1225000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>70.54545454545455</v>
-      </c>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>24.68</v>
+        <v>30.14285714285714</v>
       </c>
       <c r="AP9" t="n">
-        <v>183.2</v>
+        <v>183.4285714285714</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>67.04000000000001</v>
+        <v>68.14285714285714</v>
       </c>
       <c r="AS9" t="n">
-        <v>1456800</v>
+        <v>1157142.857142857</v>
       </c>
       <c r="AT9" t="n">
-        <v>72.84</v>
+        <v>68.14285714285714</v>
       </c>
       <c r="AU9" t="n">
-        <v>25.10526315789474</v>
+        <v>25.88888888888889</v>
       </c>
       <c r="AV9" t="n">
-        <v>182.9473684210526</v>
+        <v>182.4444444444445</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>65.10526315789474</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="AY9" t="n">
-        <v>1163947.368421053</v>
+        <v>1959722.222222222</v>
       </c>
       <c r="AZ9" t="n">
-        <v>69.42105263157895</v>
+        <v>72.94444444444444</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
@@ -2329,6 +2323,366 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45536.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massimi l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renzo barbera
+  palermo </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>36349</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25787</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>51</v>
+      </c>
+      <c r="N10" t="n">
+        <v>49</v>
+      </c>
+      <c r="O10" t="n">
+        <v>22</v>
+      </c>
+      <c r="P10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>24.63636363636364</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>66.11111111111111</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1086111.111111111</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>24.34782608695652</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>184.3913043478261</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>69.08695652173913</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2328260.869565217</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>74.47826086956522</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>24.22222222222222</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>182.1111111111111</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>66.38888888888889</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1383333.333333333</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio alberto picco
+  la spezia </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>11466</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7573</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>46</v>
+      </c>
+      <c r="N11" t="n">
+        <v>54</v>
+      </c>
+      <c r="O11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>17</v>
+      </c>
+      <c r="T11" t="n">
+        <v>21</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>65.33333333333333</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1430555.555555556</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>26.34782608695652</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>185.2608695652174</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>66.78260869565217</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1183695.652173913</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>69.78260869565217</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2775000</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN9"/>
+  <dimension ref="A1:BN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,82 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.54166666666</v>
+        <v>45551.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">di bello m 
+          <t xml:space="preserve">zufferli l 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio carlo castellani
-  empoli </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16284</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>70634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>34000</v>
+      </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.38</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="M2" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="N2" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,208 +856,196 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>24.09090909090909</v>
+        <v>25.09090909090909</v>
       </c>
       <c r="AD2" t="n">
-        <v>184.7272727272727</v>
+        <v>181.4545454545455</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.81818181818181</v>
+        <v>77.81818181818181</v>
       </c>
       <c r="AG2" t="n">
-        <v>2917272.727272727</v>
+        <v>19609090.90909091</v>
       </c>
       <c r="AH2" t="n">
-        <v>74.81818181818181</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="n">
-        <v>25.22222222222222</v>
+        <v>24.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>184.4444444444445</v>
+        <v>183.7</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>81.11111111111111</v>
+        <v>71.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>35333333.33333334</v>
+        <v>4050000</v>
       </c>
       <c r="AN2" t="n">
-        <v>84.11111111111111</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>23.52941176470588</v>
+        <v>25.44</v>
       </c>
       <c r="AP2" t="n">
-        <v>183.6470588235294</v>
+        <v>182.64</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.058823529411765</v>
+        <v>1.52</v>
       </c>
       <c r="AR2" t="n">
-        <v>68.64705882352941</v>
+        <v>74.48</v>
       </c>
       <c r="AS2" t="n">
-        <v>3054411.764705882</v>
+        <v>10674000</v>
       </c>
       <c r="AT2" t="n">
-        <v>74.29411764705883</v>
+        <v>78.36</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.75</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AV2" t="n">
-        <v>184.25</v>
+        <v>184</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.625</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>77</v>
+        <v>69.72727272727273</v>
       </c>
       <c r="AY2" t="n">
-        <v>18890625</v>
+        <v>2980681.818181818</v>
       </c>
       <c r="AZ2" t="n">
-        <v>81.625</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>343</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>12325000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>373</v>
-      </c>
+        <v>76.09090909090909</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>29.5</v>
+        <v>24.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>188.5</v>
+        <v>184</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK2" t="n">
         <v>2</v>
       </c>
       <c r="BL2" t="n">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="BM2" t="n">
-        <v>54500000</v>
+        <v>10900000</v>
       </c>
       <c r="BN2" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.41666666666</v>
+        <v>45551.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">piccinini m 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe sinigaglia
-  como </t>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>13602</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>27906</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17586</v>
+      </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="L3" t="n">
-        <v>1.74</v>
+        <v>2.52</v>
       </c>
       <c r="M3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1072,201 +1062,217 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3875000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>78.40000000000001</v>
+      </c>
       <c r="AI3" t="n">
-        <v>25.63636363636364</v>
+        <v>25.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>186.7272727272727</v>
+        <v>187</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.363636363636364</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>76.54545454545455</v>
+        <v>73</v>
       </c>
       <c r="AM3" t="n">
-        <v>11609090.90909091</v>
+        <v>4360000</v>
       </c>
       <c r="AN3" t="n">
-        <v>79.54545454545455</v>
+        <v>76.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>26.5</v>
+        <v>23.04545454545455</v>
       </c>
       <c r="AP3" t="n">
-        <v>181.8846153846154</v>
+        <v>182.7272727272727</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.461538461538461</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>72.30769230769231</v>
+        <v>66.18181818181819</v>
       </c>
       <c r="AS3" t="n">
-        <v>4776923.076923077</v>
+        <v>2434772.727272727</v>
       </c>
       <c r="AT3" t="n">
-        <v>74.76923076923077</v>
+        <v>73.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>22.5</v>
+        <v>25.34782608695652</v>
       </c>
       <c r="AV3" t="n">
-        <v>184.1</v>
+        <v>183.304347826087</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.1</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AX3" t="n">
-        <v>72.06666666666666</v>
+        <v>71.04347826086956</v>
       </c>
       <c r="AY3" t="n">
-        <v>6048333.333333333</v>
+        <v>3195652.173913043</v>
       </c>
       <c r="AZ3" t="n">
-        <v>79.93333333333334</v>
+        <v>75.47826086956522</v>
       </c>
       <c r="BA3" t="n">
-        <v>29.5</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="BB3" t="n">
-        <v>189.5</v>
+        <v>184</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="BF3" t="n">
-        <v>32000000</v>
+        <v>8900000</v>
       </c>
       <c r="BG3" t="n">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="BH3" t="n">
-        <v>22.33333333333333</v>
+        <v>29</v>
       </c>
       <c r="BI3" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>216</v>
+        <v>79</v>
       </c>
       <c r="BM3" t="n">
-        <v>29400000</v>
+        <v>17500000</v>
       </c>
       <c r="BN3" t="n">
-        <v>237</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OGCsGku2</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.41666666666</v>
+        <v>45550.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pezzuto i 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio san nicola
-  bari </t>
+          <t xml:space="preserve">brianteo
+  monza </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58270</v>
+        <v>17102</v>
       </c>
       <c r="F4" t="n">
-        <v>14003</v>
+        <v>14541</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>z7WK5Pwb</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.89</v>
+      </c>
       <c r="M4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>nZ24J27c</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>hrkecaMB</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>77</v>
       </c>
       <c r="X4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1276,157 +1282,217 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
       <c r="AC4" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="AD4" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5430000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>27.45454545454545</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>181.3636363636364</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.181818181818182</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>81.81818181818181</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>32681818.18181818</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>84.09090909090909</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26.30769230769231</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>181.8461538461538</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.307692307692308</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>72.07692307692308</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4440384.615384615</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>75.69230769230769</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>185.96</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>79.36</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>26080000</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>226</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>22900000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>232</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI4" t="n">
         <v>183</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1510000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>184</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.066666666666667</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1131000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>72</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jN4TwgX8</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.41666666666</v>
+        <v>45550.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ghersini d 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio mario rigamonti
-  brescia </t>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19500</v>
+        <v>16416</v>
       </c>
       <c r="F5" t="n">
-        <v>5715</v>
+        <v>15733</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>jci0qO9B</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N5" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>lb1XFX3n</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>77</v>
       </c>
       <c r="X5" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1436,185 +1502,217 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>25.11111111111111</v>
+        <v>25.45454545454545</v>
       </c>
       <c r="AD5" t="n">
-        <v>184.2222222222222</v>
+        <v>184.8181818181818</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AF5" t="n">
-        <v>66.33333333333333</v>
+        <v>72.63636363636364</v>
       </c>
       <c r="AG5" t="n">
-        <v>1247222.222222222</v>
+        <v>4781818.181818182</v>
       </c>
       <c r="AH5" t="n">
-        <v>70.77777777777777</v>
+        <v>75.81818181818181</v>
       </c>
       <c r="AI5" t="n">
-        <v>23.22222222222222</v>
+        <v>27.36363636363636</v>
       </c>
       <c r="AJ5" t="n">
-        <v>184.1111111111111</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AL5" t="n">
-        <v>67.33333333333333</v>
+        <v>81.27272727272727</v>
       </c>
       <c r="AM5" t="n">
-        <v>1819444.444444444</v>
+        <v>34109090.90909091</v>
       </c>
       <c r="AN5" t="n">
-        <v>74</v>
+        <v>82.45454545454545</v>
       </c>
       <c r="AO5" t="n">
-        <v>23.16666666666667</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AP5" t="n">
-        <v>181</v>
+        <v>183.4444444444445</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AR5" t="n">
-        <v>65.20833333333333</v>
+        <v>68.14814814814815</v>
       </c>
       <c r="AS5" t="n">
-        <v>1186458.333333333</v>
+        <v>2123148.148148148</v>
       </c>
       <c r="AT5" t="n">
-        <v>72.29166666666667</v>
+        <v>72.51851851851852</v>
       </c>
       <c r="AU5" t="n">
-        <v>22.17391304347826</v>
+        <v>25.125</v>
       </c>
       <c r="AV5" t="n">
-        <v>185.4782608695652</v>
+        <v>181.7916666666667</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>1.625</v>
       </c>
       <c r="AX5" t="n">
-        <v>64.52173913043478</v>
+        <v>76.70833333333333</v>
       </c>
       <c r="AY5" t="n">
-        <v>1404347.826086957</v>
+        <v>17009375</v>
       </c>
       <c r="AZ5" t="n">
-        <v>74.43478260869566</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>79.58333333333333</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>185</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>73</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>170</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>81</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUiGUlfe</t>
+          <t>zFWqD4KM</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.41666666666</v>
+        <v>45550.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">feliciani e 
+          <t xml:space="preserve">sacchi j  l 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pier cesare tombolato
-  cittadella </t>
+          <t xml:space="preserve">gewiss stadium
+  bergamo </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7623</v>
+        <v>24950</v>
       </c>
       <c r="F6" t="n">
-        <v>2269</v>
+        <v>22705</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.87</v>
+      </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="N6" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
         <v>13</v>
       </c>
       <c r="P6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>nsYMfLJM</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>77</v>
       </c>
       <c r="X6" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1624,171 +1722,217 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>78</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>81.8</v>
+      </c>
       <c r="AI6" t="n">
-        <v>27.3</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AJ6" t="n">
-        <v>178.8</v>
+        <v>182.4444444444445</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AL6" t="n">
-        <v>67.2</v>
+        <v>76.77777777777777</v>
       </c>
       <c r="AM6" t="n">
-        <v>1215000</v>
+        <v>13411111.11111111</v>
       </c>
       <c r="AN6" t="n">
-        <v>69.59999999999999</v>
+        <v>80.11111111111111</v>
       </c>
       <c r="AO6" t="n">
-        <v>24.33333333333333</v>
+        <v>26.42105263157895</v>
       </c>
       <c r="AP6" t="n">
-        <v>179.5555555555555</v>
+        <v>186.6842105263158</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="AR6" t="n">
-        <v>64.83333333333333</v>
+        <v>75.21052631578948</v>
       </c>
       <c r="AS6" t="n">
-        <v>1116388.888888889</v>
+        <v>11618947.36842105</v>
       </c>
       <c r="AT6" t="n">
-        <v>71.77777777777777</v>
+        <v>78.73684210526316</v>
       </c>
       <c r="AU6" t="n">
-        <v>25.66666666666667</v>
+        <v>23.07407407407407</v>
       </c>
       <c r="AV6" t="n">
-        <v>182.6190476190476</v>
+        <v>184.6296296296296</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>1.296296296296296</v>
       </c>
       <c r="AX6" t="n">
-        <v>66.71428571428571</v>
+        <v>73.55555555555556</v>
       </c>
       <c r="AY6" t="n">
-        <v>1319047.619047619</v>
+        <v>9445370.370370371</v>
       </c>
       <c r="AZ6" t="n">
-        <v>70.95238095238095</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+        <v>80.22222222222223</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>309</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>64200000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>326</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>79</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CjYAjWGE</t>
+          <t>4WHcOkpL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.41666666666</v>
+        <v>45550.41666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">perenzoni d 
+          <t xml:space="preserve">colombo a 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giovanni zini
-  cremona </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20641</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>28177</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24277</v>
+      </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>KUzfp5N3</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>re6VD39b</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.61</v>
+      </c>
       <c r="M7" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>O6SinSSs</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>77</v>
       </c>
       <c r="X7" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1798,183 +1942,217 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>183.9</v>
+        <v>185.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG7" t="n">
-        <v>2280000</v>
+        <v>9900000</v>
       </c>
       <c r="AH7" t="n">
-        <v>74</v>
+        <v>77.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>24.2</v>
+        <v>24.625</v>
       </c>
       <c r="AJ7" t="n">
-        <v>185.5</v>
+        <v>185.375</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AL7" t="n">
-        <v>66.90000000000001</v>
+        <v>71.375</v>
       </c>
       <c r="AM7" t="n">
-        <v>1465000</v>
+        <v>5228125</v>
       </c>
       <c r="AN7" t="n">
-        <v>71.7</v>
+        <v>76.625</v>
       </c>
       <c r="AO7" t="n">
-        <v>25.21739130434782</v>
+        <v>24.48</v>
       </c>
       <c r="AP7" t="n">
-        <v>184.6521739130435</v>
+        <v>185.32</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.043478260869565</v>
+        <v>1.24</v>
       </c>
       <c r="AR7" t="n">
-        <v>69.04347826086956</v>
+        <v>72.12</v>
       </c>
       <c r="AS7" t="n">
-        <v>1947826.086956522</v>
+        <v>7209000</v>
       </c>
       <c r="AT7" t="n">
-        <v>73.08695652173913</v>
+        <v>77.28</v>
       </c>
       <c r="AU7" t="n">
-        <v>26.13636363636364</v>
+        <v>23.73684210526316</v>
       </c>
       <c r="AV7" t="n">
-        <v>184.2272727272727</v>
+        <v>184.7368421052632</v>
       </c>
       <c r="AW7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>67.31818181818181</v>
+        <v>68</v>
       </c>
       <c r="AY7" t="n">
-        <v>1448863.636363636</v>
+        <v>2302631.578947369</v>
       </c>
       <c r="AZ7" t="n">
-        <v>71.72727272727273</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
+        <v>73.47368421052632</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>222</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>245</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>350</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>393</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>b7WIlAoR</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.41666666666</v>
+        <v>45550.3125</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">giua a 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio romeo menti
-  castellammare di stabia </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13000</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>36599</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33009</v>
+      </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>n38Nktmn</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.32</v>
+      </c>
       <c r="M8" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="N8" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
         <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>tvh4IkLf</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Wn0poKgt</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>77</v>
       </c>
       <c r="X8" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1982,159 +2160,219 @@
       <c r="Z8" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>184.6363636363636</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>72.36363636363636</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4109090.909090909</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>76.45454545454545</v>
+      </c>
       <c r="AI8" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>183.5454545454545</v>
+        <v>182.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>70.09090909090909</v>
+        <v>77.3</v>
       </c>
       <c r="AM8" t="n">
-        <v>2581818.181818182</v>
+        <v>22942500</v>
       </c>
       <c r="AN8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>25.61111111111111</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>184.3888888888889</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5415277.777777778</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>75.05555555555556</v>
+      </c>
       <c r="AU8" t="n">
-        <v>24.56</v>
+        <v>25.95652173913043</v>
       </c>
       <c r="AV8" t="n">
-        <v>183</v>
+        <v>181.7826086956522</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>1.608695652173913</v>
       </c>
       <c r="AX8" t="n">
-        <v>70.44</v>
+        <v>77.82608695652173</v>
       </c>
       <c r="AY8" t="n">
-        <v>3306000</v>
+        <v>20666304.34782609</v>
       </c>
       <c r="AZ8" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
+        <v>80.78260869565217</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>350</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>29450000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>397</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>173</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>77</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>S2b7WAPr</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45548.64583333334</v>
+        <v>45549.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">monaldi m 
+          <t xml:space="preserve">di marco d 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23860</v>
+        <v>80018</v>
       </c>
       <c r="F9" t="n">
-        <v>13974</v>
+        <v>71273</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>xddf1qfh</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>MBn63swN</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.43</v>
+      </c>
       <c r="M9" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O9" t="n">
         <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>77</v>
       </c>
       <c r="X9" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -2142,86 +2380,850 @@
       <c r="Z9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>24.77777777777778</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>186.1111111111111</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>80.77777777777777</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>35611111.11111111</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>83.88888888888889</v>
+      </c>
       <c r="AI9" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>181.9</v>
+        <v>183.5</v>
       </c>
       <c r="AK9" t="n">
         <v>1.1</v>
       </c>
       <c r="AL9" t="n">
-        <v>68.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AM9" t="n">
-        <v>1655000</v>
+        <v>3360000</v>
       </c>
       <c r="AN9" t="n">
-        <v>71.5</v>
+        <v>75.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>24.125</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
-        <v>184.375</v>
+        <v>183.3478260869565</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>1.478260869565217</v>
       </c>
       <c r="AR9" t="n">
-        <v>68.25</v>
+        <v>76.43478260869566</v>
       </c>
       <c r="AS9" t="n">
-        <v>2471875</v>
+        <v>22591304.34782609</v>
       </c>
       <c r="AT9" t="n">
-        <v>73</v>
+        <v>83.08695652173913</v>
       </c>
       <c r="AU9" t="n">
-        <v>25.7</v>
+        <v>23.65</v>
       </c>
       <c r="AV9" t="n">
-        <v>182.9</v>
+        <v>180.35</v>
       </c>
       <c r="AW9" t="n">
         <v>1.05</v>
       </c>
       <c r="AX9" t="n">
-        <v>65.8</v>
+        <v>67.3</v>
       </c>
       <c r="AY9" t="n">
-        <v>1133750</v>
+        <v>2212250</v>
       </c>
       <c r="AZ9" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>392</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>97900000</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>404</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>177</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>j5BcsSw1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15083</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>70</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>17</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>186</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>67.90909090909091</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1756818.181818182</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>72.72727272727273</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>26.05555555555556</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>67.61111111111111</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1909722.222222222</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>184.55</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1092500</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WWCyxX1L</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2777</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>41</v>
+      </c>
+      <c r="N11" t="n">
+        <v>59</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="n">
+        <v>14</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>64.33333333333333</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1012500</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>23.04347826086957</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>184.7826086956522</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.260869565217391</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>67.95652173913044</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3011956.52173913</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>76.04347826086956</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WfeOSSO7</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8171</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N12" t="n">
+        <v>55</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>17</v>
+      </c>
+      <c r="T12" t="n">
+        <v>17</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>77</v>
+      </c>
+      <c r="X12" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1227500</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>180.7083333333333</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>65.95833333333333</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1272916.666666667</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>72.16666666666667</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2083125</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>73.125</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IiDkql9l</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8665</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>59</v>
+      </c>
+      <c r="N13" t="n">
+        <v>41</v>
+      </c>
+      <c r="O13" t="n">
+        <v>22</v>
+      </c>
+      <c r="P13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>77</v>
+      </c>
+      <c r="X13" t="n">
+        <v>774</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>184.0909090909091</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>67.09090909090909</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1434090.909090909</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>71.09090909090909</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1113500</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>27.44444444444444</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>959722.2222222222</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>185.3888888888889</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>65.61111111111111</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,190 +600,170 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>yellow_cards_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>yellow_cards_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>total_passes_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>total_passes_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>red_cards_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>red_cards_away</t>
-        </is>
-      </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>attacks_home</t>
+          <t>clearances_completed_home</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>attacks_away</t>
+          <t>clearances_completed_away</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>dangerous_attacks_home</t>
+          <t>id_team_home_rival_team</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>dangerous_attacks_away</t>
+          <t>id_team_away_rival_team</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>crosses_completed_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>crosses_completed_away</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_home</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
@@ -792,1093 +772,1087 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45559.65625</v>
+        <v>45563.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
+          <t xml:space="preserve">rapuano a 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gewiss stadium
-  bergamo </t>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24950</v>
+        <v>38279</v>
       </c>
       <c r="F2" t="n">
-        <v>22977</v>
+        <v>27126</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>36</v>
+      </c>
+      <c r="N2" t="n">
+        <v>64</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="Z2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA2" t="n">
         <v>3</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M2" t="n">
-        <v>59</v>
-      </c>
-      <c r="N2" t="n">
-        <v>41</v>
-      </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P2" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>17</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD2" t="n">
         <v>20</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
       </c>
       <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
         <v>3</v>
       </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
         <v>3</v>
       </c>
-      <c r="AK2" t="n">
-        <v>560</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>409</v>
-      </c>
       <c r="AM2" t="n">
-        <v>456</v>
+        <v>296</v>
       </c>
       <c r="AN2" t="n">
-        <v>308</v>
-      </c>
-      <c r="AO2" t="inlineStr">
+        <v>522</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>225</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>454</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
         <is>
           <t>EJLKYOzb</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="AS2" t="n">
         <v>77</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
         <v>771</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>8Sa8HInO</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
+      <c r="BA2" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>185.1818181818182</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>74.72727272727273</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>26818.18181818182</v>
       </c>
       <c r="BE2" t="n">
-        <v>26.18181818181818</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="BF2" t="n">
-        <v>187.2727272727273</v>
+        <v>186.5454545454545</v>
       </c>
       <c r="BG2" t="n">
-        <v>78.72727272727273</v>
+        <v>77.45454545454545</v>
       </c>
       <c r="BH2" t="n">
-        <v>44000</v>
+        <v>40272.72727272727</v>
       </c>
       <c r="BI2" t="n">
-        <v>25.125</v>
+        <v>22.7</v>
       </c>
       <c r="BJ2" t="n">
-        <v>183.375</v>
+        <v>185.8</v>
       </c>
       <c r="BK2" t="n">
-        <v>74.25</v>
+        <v>71.86666666666666</v>
       </c>
       <c r="BL2" t="n">
-        <v>29000</v>
+        <v>16766.66666666667</v>
       </c>
       <c r="BM2" t="n">
-        <v>25.82608695652174</v>
+        <v>26.16</v>
       </c>
       <c r="BN2" t="n">
-        <v>184.1304347826087</v>
+        <v>185.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>75.52173913043478</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="BP2" t="n">
-        <v>33956.52173913043</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>26.88235294117647</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>182.7647058823529</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>72.23529411764706</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>17588.23529411765</v>
+        <v>34160</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h8xCR9dC</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45561.66666666666</v>
+        <v>45563.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">collu g 
+          <t xml:space="preserve">colombo a 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio diego armando maradona
-  naples </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>54726</v>
+        <v>36599</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>n38Nktmn</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.75</v>
+      </c>
       <c r="M3" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="N3" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>7</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>8</v>
       </c>
       <c r="U3" t="n">
         <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
       </c>
       <c r="AG3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH3" t="n">
         <v>14</v>
       </c>
-      <c r="AH3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>649</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>334</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>549</v>
+        <v>355</v>
       </c>
       <c r="AN3" t="n">
-        <v>243</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Wn0poKgt</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
+        <v>697</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>267</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>577</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AS3" t="n">
         <v>77</v>
       </c>
-      <c r="AR3" t="n">
-        <v>773</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
       <c r="AT3" t="n">
+        <v>771</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>20242025</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>pfo9H1Wp</t>
-        </is>
-      </c>
-      <c r="BE3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>179.7</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>45800</v>
-      </c>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>24700</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="n">
+        <v>24.23809523809524</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>185.3809523809524</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>68.76190476190476</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>13952.38095238095</v>
+      </c>
       <c r="BM3" t="n">
-        <v>26.04</v>
+        <v>24.3125</v>
       </c>
       <c r="BN3" t="n">
-        <v>184.36</v>
+        <v>184.625</v>
       </c>
       <c r="BO3" t="n">
-        <v>79.23999999999999</v>
+        <v>78.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>72880</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>25.90476190476191</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>182.4761904761905</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>70.0952380952381</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>7095.238095238095</v>
+        <v>64625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OE5MGhrf</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45561.5625</v>
+        <v>45563.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">dionisi f 
+          <t xml:space="preserve">sacchi j  l 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brianteo
-  monza </t>
+          <t xml:space="preserve">bluenergy stadium   stadio friuli
+  udine </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17102</v>
+        <v>25144</v>
       </c>
       <c r="F4" t="n">
-        <v>3782</v>
+        <v>24611</v>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>jci0qO9B</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.89</v>
+      </c>
       <c r="M4" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
         <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>8</v>
       </c>
       <c r="U4" t="n">
         <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
         <v>7</v>
       </c>
       <c r="Z4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>634</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>531</v>
+        <v>416</v>
       </c>
       <c r="AN4" t="n">
-        <v>359</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>lb1XFX3n</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
+        <v>648</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>346</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>583</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AS4" t="n">
         <v>77</v>
       </c>
-      <c r="AR4" t="n">
-        <v>773</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
       <c r="AT4" t="n">
+        <v>771</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>184.7777777777778</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15888.88888888889</v>
       </c>
       <c r="BE4" t="n">
-        <v>27.22222222222222</v>
+        <v>28.09090909090909</v>
       </c>
       <c r="BF4" t="n">
-        <v>182.7777777777778</v>
+        <v>183.1818181818182</v>
       </c>
       <c r="BG4" t="n">
-        <v>72</v>
+        <v>82.90909090909091</v>
       </c>
       <c r="BH4" t="n">
-        <v>29444.44444444445</v>
-      </c>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
+        <v>91545.45454545454</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>22.78947368421053</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>185.4736842105263</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>69.73684210526316</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>10000</v>
+      </c>
       <c r="BM4" t="n">
-        <v>26.05263157894737</v>
+        <v>26.58333333333333</v>
       </c>
       <c r="BN4" t="n">
-        <v>184.6315789473684</v>
+        <v>185.0416666666667</v>
       </c>
       <c r="BO4" t="n">
-        <v>72.10526315789474</v>
+        <v>78.79166666666667</v>
       </c>
       <c r="BP4" t="n">
-        <v>27315.78947368421</v>
-      </c>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
+        <v>65291.66666666666</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>baMp22np</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45560.66666666666</v>
+        <v>45562.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">zufferli l 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36599</v>
+        <v>80018</v>
       </c>
       <c r="F5" t="n">
-        <v>28575</v>
+        <v>71103</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>57</v>
+      </c>
+      <c r="N5" t="n">
+        <v>43</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
         <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>35</v>
-      </c>
-      <c r="N5" t="n">
-        <v>65</v>
-      </c>
-      <c r="O5" t="n">
-        <v>11</v>
-      </c>
-      <c r="P5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>7</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="n">
         <v>5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>19</v>
-      </c>
       <c r="AH5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>288</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>524</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>182</v>
+        <v>497</v>
       </c>
       <c r="AN5" t="n">
-        <v>388</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>AZ1NG9tC</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
+        <v>368</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>458</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>328</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="AS5" t="n">
         <v>77</v>
       </c>
-      <c r="AR5" t="n">
-        <v>773</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
       <c r="AT5" t="n">
+        <v>771</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>96</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>128</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>48</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>70200</v>
       </c>
       <c r="BE5" t="n">
-        <v>26.63636363636364</v>
+        <v>24.375</v>
       </c>
       <c r="BF5" t="n">
-        <v>183.6363636363636</v>
+        <v>184.625</v>
       </c>
       <c r="BG5" t="n">
-        <v>72.54545454545455</v>
+        <v>71.875</v>
       </c>
       <c r="BH5" t="n">
-        <v>17818.18181818182</v>
-      </c>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
+        <v>11750</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>183.7083333333333</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>75.70833333333333</v>
+      </c>
       <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>22.73913043478261</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="BN5" t="n">
-        <v>186.3913043478261</v>
+        <v>180.9444444444445</v>
       </c>
       <c r="BO5" t="n">
-        <v>69.78260869565217</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>18782.60869565217</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>26.47826086956522</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>181.4347826086957</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>68.82608695652173</v>
-      </c>
-      <c r="BT5" t="inlineStr"/>
+        <v>68.27777777777777</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>xCj1xWPj</t>
+          <t>jwmmlzio</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45560.5625</v>
+        <v>45563.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">marchetti m 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25144</v>
+        <v>58270</v>
       </c>
       <c r="F6" t="n">
-        <v>4940</v>
+        <v>17538</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Mq05g4BP</t>
+          <t>p84TeBhA</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
         <v>4</v>
       </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
         <v>3</v>
       </c>
       <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" t="n">
         <v>4</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
+        <v>12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y6" t="n">
         <v>7</v>
       </c>
-      <c r="W6" t="n">
-        <v>15</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>6</v>
-      </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE6" t="n">
         <v>3</v>
       </c>
-      <c r="AC6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
         <v>2</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>537</v>
-      </c>
       <c r="AL6" t="n">
-        <v>496</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>433</v>
+        <v>328</v>
       </c>
       <c r="AN6" t="n">
-        <v>390</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>OjWmexQb</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
+        <v>329</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>266</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>267</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AS6" t="n">
         <v>77</v>
       </c>
-      <c r="AR6" t="n">
-        <v>773</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1</v>
-      </c>
       <c r="AT6" t="n">
+        <v>774</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1</v>
-      </c>
       <c r="AW6" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>84</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>35</v>
+        <v>16</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="BE6" t="n">
-        <v>22.375</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>183.125</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>70.375</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>10125</v>
-      </c>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="n">
+        <v>27.375</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>184.875</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>5625</v>
+      </c>
       <c r="BM6" t="n">
-        <v>24.73684210526316</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="BN6" t="n">
-        <v>187.3684210526316</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="BO6" t="n">
-        <v>70.05263157894737</v>
+        <v>66.44444444444444</v>
       </c>
       <c r="BP6" t="n">
-        <v>14789.47368421053</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>181.05</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>70.25</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>12000</v>
+        <v>9444.444444444445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>h2uVDr1f</t>
+          <t>vaTsAHD4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45560.45833333334</v>
+        <v>45563.41666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">rutella d 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
@@ -1892,157 +1866,145 @@
         <v>14869</v>
       </c>
       <c r="F7" t="n">
-        <v>3347</v>
+        <v>2280</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>roasMsOT</t>
+          <t>hG4fg4z3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>xddf1qfh</t>
+          <t>6ulJbMCe</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N7" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O7" t="n">
+        <v>17</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>17</v>
+      </c>
+      <c r="X7" t="n">
         <v>12</v>
       </c>
-      <c r="P7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="Y7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE7" t="n">
         <v>4</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AF7" t="n">
         <v>6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>20</v>
-      </c>
-      <c r="X7" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>4</v>
       </c>
       <c r="AG7" t="n">
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="n">
         <v>3</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>495</v>
-      </c>
       <c r="AL7" t="n">
-        <v>474</v>
+        <v>5</v>
       </c>
       <c r="AM7" t="n">
-        <v>354</v>
+        <v>444</v>
       </c>
       <c r="AN7" t="n">
-        <v>324</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>GfucctAF</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
+        <v>357</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>357</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>265</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AS7" t="n">
         <v>77</v>
       </c>
-      <c r="AR7" t="n">
-        <v>773</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1</v>
-      </c>
       <c r="AT7" t="n">
+        <v>774</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>105</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr"/>
@@ -2053,700 +2015,432 @@
       <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr"/>
       <c r="BM7" t="n">
-        <v>25.17647058823529</v>
+        <v>27.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>186.4117647058823</v>
+        <v>181.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>68.52941176470588</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>3294.117647058823</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>187</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>6000</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="BP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SG7bDmCr</t>
+          <t>4USV4sgM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45559.66666666666</v>
+        <v>45563.41666666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ghersini d 
+          <t xml:space="preserve">piccinini m 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico di torino
-  turin </t>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28177</v>
+        <v>21525</v>
       </c>
       <c r="F8" t="n">
-        <v>12334</v>
+        <v>5405</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>re6VD39b</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N8" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
       </c>
       <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>15</v>
-      </c>
-      <c r="X8" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>506</v>
-      </c>
       <c r="AL8" t="n">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="AM8" t="n">
-        <v>381</v>
+        <v>540</v>
       </c>
       <c r="AN8" t="n">
-        <v>290</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
+        <v>352</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>456</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>274</v>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AS8" t="n">
         <v>77</v>
       </c>
-      <c r="AR8" t="n">
-        <v>773</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1</v>
-      </c>
       <c r="AT8" t="n">
+        <v>774</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>20242025</v>
       </c>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="AX8" t="n">
-        <v>88</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>56</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>39</v>
+        <v>23</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>23.44444444444444</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
+        <v>183.6666666666667</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>11000</v>
       </c>
       <c r="BE8" t="n">
-        <v>25.4</v>
+        <v>25.25</v>
       </c>
       <c r="BF8" t="n">
-        <v>185.3</v>
+        <v>184.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>72.8</v>
+        <v>67.875</v>
       </c>
       <c r="BH8" t="n">
-        <v>26700</v>
-      </c>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
+        <v>4875</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>183.0555555555555</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>68.5</v>
+      </c>
       <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="n">
-        <v>24.23809523809524</v>
+        <v>26.53333333333333</v>
       </c>
       <c r="BN8" t="n">
-        <v>185.5238095238095</v>
+        <v>185.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>72.52380952380952</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="BP8" t="n">
-        <v>25714.28571428571</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>185.5454545454545</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>70.04545454545455</v>
-      </c>
-      <c r="BT8" t="inlineStr"/>
+        <v>3733.333333333333</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WjBv9U0S</t>
+          <t>8vLb6ZCT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45559.5625</v>
+        <v>45562.64583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonacina k 
+          <t xml:space="preserve">crezzini v 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">unipol domus
-  cagliari </t>
+          <t xml:space="preserve">stadio pier cesare tombolato
+  cittadella </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16416</v>
+        <v>7623</v>
       </c>
       <c r="F9" t="n">
-        <v>11017</v>
+        <v>3204</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>C0yUqo8c</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>KUzfp5N3</t>
+          <t>pfo9H1Wp</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
         <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>12</v>
+      </c>
+      <c r="X9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y9" t="n">
         <v>8</v>
       </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>19</v>
-      </c>
-      <c r="X9" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>11</v>
-      </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
         <v>3</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL9" t="n">
         <v>3</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>469</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>502</v>
-      </c>
       <c r="AM9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN9" t="n">
-        <v>422</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
+        <v>396</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>268</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>307</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AS9" t="n">
         <v>77</v>
       </c>
-      <c r="AR9" t="n">
-        <v>773</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1</v>
-      </c>
       <c r="AT9" t="n">
+        <v>774</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
-        <v>77</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="n">
-        <v>26</v>
+        <v>24.125</v>
       </c>
       <c r="BF9" t="n">
-        <v>183.5555555555555</v>
+        <v>184.375</v>
       </c>
       <c r="BG9" t="n">
-        <v>70.33333333333333</v>
+        <v>67</v>
       </c>
       <c r="BH9" t="n">
-        <v>17000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>183.25</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>66.375</v>
-      </c>
+        <v>4250</v>
+      </c>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
       <c r="BM9" t="n">
-        <v>25.52173913043478</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="BN9" t="n">
-        <v>181.6086956521739</v>
+        <v>185.5833333333333</v>
       </c>
       <c r="BO9" t="n">
-        <v>70.43478260869566</v>
+        <v>65.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>16652.17391304348</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>28.23076923076923</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>184.0769230769231</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>71.23076923076923</v>
-      </c>
-      <c r="BT9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>O2Xm0vko</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45559.45833333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">perenzoni d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadio via del mare
-  lecce </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>40670</v>
-      </c>
-      <c r="F10" t="n">
-        <v>13951</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>QDdvI0zl</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>62</v>
-      </c>
-      <c r="N10" t="n">
-        <v>38</v>
-      </c>
-      <c r="O10" t="n">
-        <v>14</v>
-      </c>
-      <c r="P10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>17</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>599</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>339</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>531</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>263</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-      <c r="AQ10" t="n">
-        <v>77</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>773</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="n">
-        <v>143</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>83</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>72</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="BE10" t="n">
-        <v>23.22222222222222</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>180.5555555555555</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>69.22222222222223</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>7444.444444444444</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>184.25</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="n">
-        <v>23.06666666666667</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>183.1333333333333</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="n">
-        <v>20.94444444444444</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>179.8888888888889</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>67.83333333333333</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>5611.111111111111</v>
+        <v>6833.333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,280 +600,350 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
           <t>red_cards_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>red_cards_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_home</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_home</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_home</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_home</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_away</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45563.65625</v>
+        <v>45564.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio renato dall ara
-  bologna </t>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38279</v>
+        <v>54726</v>
       </c>
       <c r="F2" t="n">
-        <v>27126</v>
+        <v>50000</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.32</v>
+        <v>1.54</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" t="n">
-        <v>23</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -882,1126 +952,1324 @@
         <v>16</v>
       </c>
       <c r="AH2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>526</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>548</v>
       </c>
       <c r="AM2" t="n">
-        <v>296</v>
+        <v>473</v>
       </c>
       <c r="AN2" t="n">
-        <v>522</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>225</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>454</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
+        <v>499</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>771</v>
       </c>
       <c r="AS2" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>771</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
         <v>20242025</v>
       </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>25.36363636363636</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>185.1818181818182</v>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
       </c>
       <c r="BC2" t="n">
-        <v>74.72727272727273</v>
+        <v>26.36363636363636</v>
       </c>
       <c r="BD2" t="n">
-        <v>26818.18181818182</v>
+        <v>184.1818181818182</v>
       </c>
       <c r="BE2" t="n">
-        <v>24.81818181818182</v>
+        <v>80.72727272727273</v>
       </c>
       <c r="BF2" t="n">
-        <v>186.5454545454545</v>
+        <v>72545.45454545454</v>
       </c>
       <c r="BG2" t="n">
-        <v>77.45454545454545</v>
+        <v>24.55555555555556</v>
       </c>
       <c r="BH2" t="n">
-        <v>40272.72727272727</v>
+        <v>184.7777777777778</v>
       </c>
       <c r="BI2" t="n">
-        <v>22.7</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="BJ2" t="n">
-        <v>185.8</v>
+        <v>24666.66666666667</v>
       </c>
       <c r="BK2" t="n">
-        <v>71.86666666666666</v>
+        <v>25.79166666666667</v>
       </c>
       <c r="BL2" t="n">
-        <v>16766.66666666667</v>
+        <v>179.75</v>
       </c>
       <c r="BM2" t="n">
-        <v>26.16</v>
+        <v>76.41666666666667</v>
       </c>
       <c r="BN2" t="n">
-        <v>185.6</v>
+        <v>53125</v>
       </c>
       <c r="BO2" t="n">
-        <v>76.23999999999999</v>
+        <v>28.84615384615385</v>
       </c>
       <c r="BP2" t="n">
-        <v>34160</v>
+        <v>180.6923076923077</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>73.23076923076923</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>35153.84615384616</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>181</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>54500</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>163</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>181</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>73</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>32250</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>292</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.54166666666</v>
+        <v>45564.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">aureliano g 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio luigi ferraris
-  genoa </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36599</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>16284</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13053</v>
+      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
         <v>3</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M3" t="n">
-        <v>34</v>
-      </c>
-      <c r="N3" t="n">
-        <v>66</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="V3" t="n">
         <v>7</v>
       </c>
-      <c r="P3" t="n">
+      <c r="W3" t="n">
+        <v>14</v>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH3" t="n">
         <v>12</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>15</v>
-      </c>
-      <c r="X3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>343</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>584</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>234</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>456</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
         <v>5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>355</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>697</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>267</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>577</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="AS3" t="n">
-        <v>77</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>771</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>20242025</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>nJbCGx2U</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="BA3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>185.6</v>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
       </c>
       <c r="BC3" t="n">
-        <v>73.5</v>
+        <v>24.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>24700</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>185.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>69.59999999999999</v>
+      </c>
       <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>179.7777777777778</v>
+      </c>
       <c r="BI3" t="n">
-        <v>24.23809523809524</v>
+        <v>74.88888888888889</v>
       </c>
       <c r="BJ3" t="n">
-        <v>185.3809523809524</v>
+        <v>39000</v>
       </c>
       <c r="BK3" t="n">
-        <v>68.76190476190476</v>
+        <v>23.35</v>
       </c>
       <c r="BL3" t="n">
-        <v>13952.38095238095</v>
+        <v>182.9</v>
       </c>
       <c r="BM3" t="n">
-        <v>24.3125</v>
+        <v>68.95</v>
       </c>
       <c r="BN3" t="n">
-        <v>184.625</v>
+        <v>17050</v>
       </c>
       <c r="BO3" t="n">
-        <v>78.25</v>
+        <v>23.77777777777778</v>
       </c>
       <c r="BP3" t="n">
-        <v>64625</v>
+        <v>181.7037037037037</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>75.07407407407408</v>
+      </c>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>8800</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>351</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>193</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>76</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bluenergy stadium   stadio friuli
-  udine </t>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25144</v>
+        <v>70634</v>
       </c>
       <c r="F4" t="n">
-        <v>24611</v>
+        <v>62165</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="L4" t="n">
-        <v>2.89</v>
+        <v>1.74</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="N4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" t="n">
         <v>6</v>
       </c>
-      <c r="U4" t="n">
-        <v>5</v>
-      </c>
-      <c r="V4" t="n">
-        <v>3</v>
-      </c>
       <c r="W4" t="n">
+        <v>15</v>
+      </c>
+      <c r="X4" t="n">
         <v>10</v>
       </c>
-      <c r="X4" t="n">
-        <v>15</v>
-      </c>
       <c r="Y4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF4" t="n">
         <v>3</v>
       </c>
-      <c r="AC4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
       <c r="AG4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH4" t="n">
         <v>13</v>
       </c>
-      <c r="AH4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2</v>
+      </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>577</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="AM4" t="n">
-        <v>416</v>
+        <v>496</v>
       </c>
       <c r="AN4" t="n">
-        <v>648</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>346</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>583</v>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
+        <v>186</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>771</v>
       </c>
       <c r="AS4" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>771</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
         <v>20242025</v>
       </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="BA4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>184.7777777777778</v>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
       </c>
       <c r="BC4" t="n">
-        <v>72.22222222222223</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="BD4" t="n">
-        <v>15888.88888888889</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="BE4" t="n">
-        <v>28.09090909090909</v>
+        <v>77.88888888888889</v>
       </c>
       <c r="BF4" t="n">
-        <v>183.1818181818182</v>
+        <v>51555.55555555555</v>
       </c>
       <c r="BG4" t="n">
-        <v>82.90909090909091</v>
+        <v>26.77777777777778</v>
       </c>
       <c r="BH4" t="n">
-        <v>91545.45454545454</v>
+        <v>182</v>
       </c>
       <c r="BI4" t="n">
-        <v>22.78947368421053</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="BJ4" t="n">
-        <v>185.4736842105263</v>
+        <v>11333.33333333333</v>
       </c>
       <c r="BK4" t="n">
-        <v>69.73684210526316</v>
+        <v>24.72222222222222</v>
       </c>
       <c r="BL4" t="n">
-        <v>10000</v>
+        <v>180.1111111111111</v>
       </c>
       <c r="BM4" t="n">
-        <v>26.58333333333333</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="BN4" t="n">
-        <v>185.0416666666667</v>
+        <v>52277.77777777778</v>
       </c>
       <c r="BO4" t="n">
-        <v>78.79166666666667</v>
+        <v>25.58823529411765</v>
       </c>
       <c r="BP4" t="n">
-        <v>65291.66666666666</v>
+        <v>184.7058823529412</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>67.70588235294117</v>
+      </c>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>155</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45562.65625</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
+          <t xml:space="preserve">giua a 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio giuseppe meazza  san siro 
-  milan </t>
+          <t xml:space="preserve">stadio giuseppe sinigaglia
+  como </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80018</v>
+        <v>13602</v>
       </c>
       <c r="F5" t="n">
-        <v>71103</v>
+        <v>9000</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="L5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="M5" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N5" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="P5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2</v>
       </c>
-      <c r="V5" t="n">
-        <v>3</v>
-      </c>
-      <c r="W5" t="n">
-        <v>13</v>
-      </c>
-      <c r="X5" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AD5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG5" t="n">
         <v>10</v>
       </c>
-      <c r="AE5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>5</v>
       </c>
-      <c r="AH5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>573</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="AM5" t="n">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="AN5" t="n">
-        <v>368</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>458</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>328</v>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
+        <v>167</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>771</v>
       </c>
       <c r="AS5" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>771</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-      <c r="BA5" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>185.8</v>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
       </c>
       <c r="BC5" t="n">
-        <v>81.40000000000001</v>
+        <v>25.125</v>
       </c>
       <c r="BD5" t="n">
-        <v>70200</v>
+        <v>183.375</v>
       </c>
       <c r="BE5" t="n">
-        <v>24.375</v>
+        <v>74.25</v>
       </c>
       <c r="BF5" t="n">
-        <v>184.625</v>
+        <v>29000</v>
       </c>
       <c r="BG5" t="n">
-        <v>71.875</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="BH5" t="n">
-        <v>11750</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="BI5" t="n">
-        <v>22.66666666666667</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="BJ5" t="n">
-        <v>183.7083333333333</v>
+        <v>15222.22222222222</v>
       </c>
       <c r="BK5" t="n">
-        <v>75.70833333333333</v>
-      </c>
-      <c r="BL5" t="inlineStr"/>
+        <v>27.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>181.45</v>
+      </c>
       <c r="BM5" t="n">
-        <v>23.16666666666667</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>180.9444444444445</v>
+        <v>19850</v>
       </c>
       <c r="BO5" t="n">
-        <v>68.27777777777777</v>
-      </c>
-      <c r="BP5" t="inlineStr"/>
+        <v>24.6</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>15050</v>
+      </c>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>185</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>13200</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>357</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jwmmlzio</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45564.3125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">marchetti m 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio san nicola
-  bari </t>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58270</v>
+        <v>28177</v>
       </c>
       <c r="F6" t="n">
-        <v>17538</v>
+        <v>23130</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.97</v>
+      </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="N6" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>14</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
-        <v>7</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE6" t="n">
         <v>4</v>
       </c>
-      <c r="W6" t="n">
-        <v>12</v>
-      </c>
-      <c r="X6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>3</v>
       </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
       <c r="AK6" t="n">
+        <v>485</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>360</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>408</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>277</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>771</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>26.625</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>184.875</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>32625</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>181.4545454545455</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>77.81818181818181</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>49454.54545454546</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>25.28571428571428</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>183.1904761904762</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>73.57142857142857</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>30476.19047619048</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>25.125</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>182</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>73.83333333333333</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>35458.33333333334</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>183</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>22000</v>
+      </c>
+      <c r="BW6" t="n">
         <v>2</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>328</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>329</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>266</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>267</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>nZ24J27c</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>Yika9O16</t>
-        </is>
-      </c>
-      <c r="AS6" t="n">
-        <v>77</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>774</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>GnizyMB7</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="n">
-        <v>27.375</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>184.875</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>5625</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>183.3333333333333</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>66.44444444444444</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>9444.444444444445</v>
+      <c r="BX6" t="n">
+        <v>143</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>187</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>78</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>38000</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vaTsAHD4</t>
+          <t>nPWk8erH</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">marcenaro m 
+          <t xml:space="preserve">chiffi d 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
-  pisa </t>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14869</v>
+        <v>23860</v>
       </c>
       <c r="F7" t="n">
-        <v>2280</v>
+        <v>12326</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>hG4fg4z3</t>
+          <t>xddf1qfh</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
+          <t>z7WK5Pwb</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="N7" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
         <v>4</v>
       </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>7</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2</v>
-      </c>
       <c r="W7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
         <v>5</v>
       </c>
       <c r="Z7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF7" t="n">
         <v>5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>239</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>545</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>196</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>491</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>6</v>
       </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>444</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>357</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>357</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>265</v>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>lSb6U6l0</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="AS7" t="n">
-        <v>77</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>774</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -2012,60 +2280,76 @@
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
+      <c r="BK7" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>186.25</v>
+      </c>
       <c r="BM7" t="n">
-        <v>27.6</v>
+        <v>69.375</v>
       </c>
       <c r="BN7" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>67</v>
-      </c>
+        <v>11875</v>
+      </c>
+      <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4USV4sgM</t>
+          <t>ID6U0Dzi</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">piccinini m 
+          <t xml:space="preserve">doveri d 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mapei stadium – citta del tricolore
-  reggio emilia </t>
+          <t xml:space="preserve">stadio romeo menti
+  castellammare di stabia </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21525</v>
+        <v>13000</v>
       </c>
       <c r="F8" t="n">
-        <v>5405</v>
+        <v>6500</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>hKSfjtsQ</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>re6VD39b</t>
+          <t>roasMsOT</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -2077,268 +2361,258 @@
         <v>41</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
       <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" t="n">
         <v>4</v>
       </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AG8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI8" t="n">
         <v>4</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>417</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>276</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>324</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="n">
         <v>25</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>540</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>352</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>456</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>274</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>O6SinSSs</t>
-        </is>
-      </c>
-      <c r="AS8" t="n">
-        <v>77</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>774</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AW8" t="n">
+      <c r="AZ8" t="n">
         <v>25</v>
       </c>
-      <c r="AX8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="BA8" t="n">
-        <v>23.44444444444444</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>183.6666666666667</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>71.11111111111111</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>11000</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4875</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>23.77777777777778</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>183.0555555555555</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>68.5</v>
-      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="n">
-        <v>26.53333333333333</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>185.4</v>
-      </c>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="n">
-        <v>68.66666666666667</v>
+        <v>22.36363636363636</v>
       </c>
       <c r="BP8" t="n">
-        <v>3733.333333333333</v>
-      </c>
+        <v>183.0909090909091</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>66.27272727272727</v>
+      </c>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8vLb6ZCT</t>
+          <t>zkyF8Pgc</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45562.64583333334</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">crezzini v 
+          <t xml:space="preserve">dionisi f 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio pier cesare tombolato
-  cittadella </t>
+          <t xml:space="preserve">stadio alberto braglia
+  modena </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7623</v>
+        <v>21092</v>
       </c>
       <c r="F9" t="n">
-        <v>3204</v>
+        <v>10101</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
+          <t>MBn63swN</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
+          <t>nJbCGx2U</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="n">
         <v>4</v>
       </c>
       <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="S9" t="n">
-        <v>7</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y9" t="n">
         <v>6</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="Z9" t="n">
         <v>6</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD9" t="n">
         <v>12</v>
-      </c>
-      <c r="X9" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2347,101 +2621,335 @@
         <v>3</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>4</v>
+      </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="AL9" t="n">
-        <v>3</v>
+        <v>367</v>
       </c>
       <c r="AM9" t="n">
-        <v>372</v>
+        <v>249</v>
       </c>
       <c r="AN9" t="n">
-        <v>396</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>268</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>307</v>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
+        <v>311</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>774</v>
       </c>
       <c r="AS9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>774</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AW9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>41</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA9" t="inlineStr">
         <is>
           <t>0M9xNN8N</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
-        <v>24.125</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>184.375</v>
-      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
-        <v>67</v>
+        <v>28.11111111111111</v>
       </c>
       <c r="BH9" t="n">
-        <v>4250</v>
-      </c>
-      <c r="BI9" t="inlineStr"/>
+        <v>182.1111111111111</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>71.11111111111111</v>
+      </c>
       <c r="BJ9" t="inlineStr"/>
       <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>185.5833333333333</v>
-      </c>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="n">
-        <v>65.25</v>
+        <v>25.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>6833.333333333333</v>
-      </c>
+        <v>184.7333333333333</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>68.06666666666666</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>82ZM63O9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>14932</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>59</v>
+      </c>
+      <c r="N10" t="n">
+        <v>41</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>19</v>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>522</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>363</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>465</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>304</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>774</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>181.375</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>14875</v>
+      </c>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>185.1666666666667</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>9583.333333333334</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>27.58333333333333</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/italy/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP2"/>
+  <dimension ref="A1:CT9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,300 +600,320 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>yellow_cards_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>yellow_cards_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>total_passes_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>total_passes_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_away</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>interceptions_home</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>interceptions_away</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_home</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_home</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_home</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
         </is>
@@ -902,299 +922,2379 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>fB59P6ff</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45586.65625</v>
+        <v>45592.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dionisi f 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi
-  verona </t>
+          <t xml:space="preserve">stadio artemio franchi
+  florence </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>39211</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>43147</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20440</v>
+      </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.83</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>0.65</v>
       </c>
       <c r="M2" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q2" t="n">
         <v>10</v>
       </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>11</v>
+      </c>
+      <c r="X2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE2" t="n">
         <v>4</v>
       </c>
-      <c r="V2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="AF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG2" t="n">
         <v>13</v>
       </c>
-      <c r="X2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AH2" t="n">
         <v>11</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>13</v>
-      </c>
       <c r="AI2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
         <v>2</v>
       </c>
-      <c r="AK2" t="n">
-        <v>480</v>
-      </c>
       <c r="AL2" t="n">
-        <v>347</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
-        <v>400</v>
+        <v>343</v>
       </c>
       <c r="AN2" t="n">
-        <v>280</v>
+        <v>547</v>
       </c>
       <c r="AO2" t="n">
-        <v>7</v>
+        <v>304</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>503</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
       </c>
       <c r="AR2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AW2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>771</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>75.22222222222223</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>39333.33333333334</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>12733333.33333333</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>81</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>40500</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>23975000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>81</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>181.8181818181818</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>75.72727272727273</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>42272.72727272727</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>10771590.90909091</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>79.72727272727273</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>177.4166666666667</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>78</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>36416.66666666666</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>22191666.66666667</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>81.58333333333333</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>232</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>142000</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>41500000</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>238</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>28</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>179</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>157</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>142000</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>159</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45592.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>80018</v>
+      </c>
+      <c r="F3" t="n">
+        <v>75000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M3" t="n">
+        <v>47</v>
+      </c>
+      <c r="N3" t="n">
+        <v>53</v>
+      </c>
+      <c r="O3" t="n">
+        <v>18</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
         <v>8</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>383</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>445</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>327</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>392</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AW3" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>771</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
+        <v>28.90909090909091</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>182.2727272727273</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>84.54545454545455</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>118363.6363636364</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>46545454.54545455</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>84.90909090909091</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.454545454545455</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>83250</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>23687500</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>83.125</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>27.36842105263158</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>185.4736842105263</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>78.78947368421052</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>77210.52631578948</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>20542105.26315789</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>81.47368421052632</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>2.157894736842105</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>186.8888888888889</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>83888.88888888889</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>17822222.22222222</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>80.88888888888889</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>249</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>313000</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>87500000</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>252</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>8</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>5</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>412</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>630000</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>199000000</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>417</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N4" t="n">
+        <v>39</v>
+      </c>
+      <c r="O4" t="n">
+        <v>18</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>550</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>352</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>486</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>276</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AW4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>771</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>43500</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>18800000</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>82</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>184.0909090909091</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>71.54545454545455</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>30818.18181818182</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>3822727.272727273</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>75.63636363636364</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>9306250</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>185.85</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>66</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>26850</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>1436250</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>71</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>162</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>117000</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>45500000</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>162</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>28.42857142857143</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>184.7142857142857</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>7</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>516</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>255000</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>34600000</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>534</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>17102</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10141</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M5" t="n">
+        <v>46</v>
+      </c>
+      <c r="N5" t="n">
+        <v>54</v>
+      </c>
+      <c r="O5" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>16</v>
+      </c>
+      <c r="X5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>347</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>416</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>273</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>338</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>CEv2hvmq</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AW5" t="n">
         <v>77</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AX5" t="n">
         <v>771</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AY5" t="n">
         <v>0</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AZ5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AY2" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>182.1111111111111</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>72.44444444444444</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>12555.55555555555</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4766666.666666667</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>22500</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6560000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>180.3636363636364</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>70.54545454545455</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>11818.18181818182</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3054545.454545455</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>75.45454545454545</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>26.22727272727273</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>182.6818181818182</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>36363.63636363636</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6665909.090909091</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>76.63636363636364</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>184.5909090909091</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>69.31818181818181</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>13545.45454545455</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>2384318.181818182</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>74.27272727272727</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>373</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>29300000</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>378</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>6</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>25</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>132</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>17000</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>143</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45592.35416666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17802</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M6" t="n">
+        <v>60</v>
+      </c>
+      <c r="N6" t="n">
+        <v>40</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>17</v>
+      </c>
+      <c r="X6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>527</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>350</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>456</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>279</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AW6" t="n">
         <v>77</v>
       </c>
-      <c r="BE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>183.4</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>22500</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>6560000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>26.52631578947368</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>182.5263157894737</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>71.73684210526316</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>11684.21052631579</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>4867368.421052632</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>75.52631578947368</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.157894736842105</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>26.625</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>70.58333333333333</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>34958.33333333334</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>5843750</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>75.25</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>185.6666666666667</v>
-      </c>
-      <c r="CC2" t="n">
+      <c r="AX6" t="n">
+        <v>771</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>26700</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2872500</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>24.04347826086957</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>183.1304347826087</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>69.04347826086956</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>22565.21739130435</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>3069565.217391304</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>74.60869565217391</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>24.70833333333333</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>17458.33333333333</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>2272916.666666667</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>25</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>188</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>145</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>48000</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>154</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>5</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>361</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>95000</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>380</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>GrV1gmkn</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">santoro a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio nicola ceravolo
+  catanzaro </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>14650</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="CD2" t="n">
-        <v>212</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>42000</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>8100000</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>221</v>
-      </c>
-      <c r="CH2" t="n">
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>54</v>
+      </c>
+      <c r="N7" t="n">
+        <v>46</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
         <v>3</v>
       </c>
-      <c r="CI2" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>181.75</v>
-      </c>
-      <c r="CK2" t="n">
+      <c r="AG7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>497</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>383</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>442</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>343</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AW7" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>774</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>29.72727272727273</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>180.3636363636364</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>67.09090909090909</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2545.454545454545</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>972727.2727272727</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>68.81818181818181</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>27.36363636363636</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>184.1818181818182</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>66.72727272727273</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3181.818181818182</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1252272.727272727</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>70.45454545454545</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>25.56521739130435</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>182.3478260869565</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>65.82608695652173</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6391.304347826087</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1170652.173913043</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>70.78260869565217</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>65.05</v>
+      </c>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="n">
+        <v>1212250</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>182</v>
+      </c>
+      <c r="CO7" t="n">
         <v>4</v>
       </c>
-      <c r="CL2" t="n">
-        <v>297</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>95000</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>25300000</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>307</v>
-      </c>
-      <c r="CP2" t="n">
+      <c r="CP7" t="n">
+        <v>270</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>11000</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>277</v>
+      </c>
+      <c r="CT7" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>z9TkrNto</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>31</v>
+      </c>
+      <c r="N8" t="n">
+        <v>69</v>
+      </c>
+      <c r="O8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>19</v>
+      </c>
+      <c r="X8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>227</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>485</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>142</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>423</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AW8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>774</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1191500</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>184.8888888888889</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>3666.666666666667</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1297222.222222222</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>65.61111111111111</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>7833.333333333333</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1495833.333333333</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>24.43478260869565</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>183.1739130434783</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>66.95652173913044</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>5260.869565217391</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>1783695.652173913</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>72.34782608695652</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>191.6666666666667</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>199</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>81000</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>222</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>24</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>183</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>137</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>148</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8COq4434</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">crezzini v 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N9" t="n">
+        <v>70</v>
+      </c>
+      <c r="O9" t="n">
+        <v>20</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>258</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>616</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>189</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>555</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+      <c r="AW9" t="n">
+        <v>77</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>774</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5300</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1722500</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>72</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>180.875</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>64.875</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2125</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>989375</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>25.23076923076923</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>184</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>69.84615384615384</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>7038.461538461538</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>2426923.076923077</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>75.80769230769231</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.038461538461539</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>27.78947368421053</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>181.0526315789474</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>66.21052631578948</v>
+      </c>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="n">
+        <v>1039736.842105263</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>69.15789473684211</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="n">
+        <v>32</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>186</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>65</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>575000</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>65</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
